--- a/society-finance/samples/ticket-sales.xlsx
+++ b/society-finance/samples/ticket-sales.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="143">
-  <si>
-    <t>Date</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="487">
+  <si>
+    <t>Order date</t>
   </si>
   <si>
     <t>Event</t>
@@ -34,7 +34,295 @@
     <t>Total paid</t>
   </si>
   <si>
-    <t>13/11/2025</t>
+    <t>2024-10-03</t>
+  </si>
+  <si>
+    <t>Thursday Social</t>
+  </si>
+  <si>
+    <t>Door entry</t>
+  </si>
+  <si>
+    <t>Door sales</t>
+  </si>
+  <si>
+    <t>£3.00</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>2024-10-17</t>
+  </si>
+  <si>
+    <t>2024-10-24</t>
+  </si>
+  <si>
+    <t>2024-10-31</t>
+  </si>
+  <si>
+    <t>2024-11-07</t>
+  </si>
+  <si>
+    <t>2024-11-14</t>
+  </si>
+  <si>
+    <t>2024-11-21</t>
+  </si>
+  <si>
+    <t>2024-11-28</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>2025-01-16</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>2025-01-30</t>
+  </si>
+  <si>
+    <t>2025-02-06</t>
+  </si>
+  <si>
+    <t>2025-02-13</t>
+  </si>
+  <si>
+    <t>2025-02-20</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>2025-03-06</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>2025-03-20</t>
+  </si>
+  <si>
+    <t>24/09/2024</t>
+  </si>
+  <si>
+    <t>Freshers Social</t>
+  </si>
+  <si>
+    <t>Entry</t>
+  </si>
+  <si>
+    <t>Rosa Evans</t>
+  </si>
+  <si>
+    <t>£5.00</t>
+  </si>
+  <si>
+    <t>24 Sep 2024</t>
+  </si>
+  <si>
+    <t>Kai Ahmed</t>
+  </si>
+  <si>
+    <t>2024-09-19</t>
+  </si>
+  <si>
+    <t>Chloe Brown</t>
+  </si>
+  <si>
+    <t>Uma Smith</t>
+  </si>
+  <si>
+    <t>Omar Jones</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>Isla Brown</t>
+  </si>
+  <si>
+    <t>20/09/2024</t>
+  </si>
+  <si>
+    <t>Nina Wilson</t>
+  </si>
+  <si>
+    <t>22 Sep 2024</t>
+  </si>
+  <si>
+    <t>Priya Green</t>
+  </si>
+  <si>
+    <t>2024-09-22</t>
+  </si>
+  <si>
+    <t>Max Hall</t>
+  </si>
+  <si>
+    <t>22/09/2024</t>
+  </si>
+  <si>
+    <t>Zara Chen</t>
+  </si>
+  <si>
+    <t>Theo Chen</t>
+  </si>
+  <si>
+    <t>Vik Jones</t>
+  </si>
+  <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
+    <t>Yusuf Smith</t>
+  </si>
+  <si>
+    <t>18 Sep 2024</t>
+  </si>
+  <si>
+    <t>Ava Ahmed</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>Lily Evans</t>
+  </si>
+  <si>
+    <t>21/09/2024</t>
+  </si>
+  <si>
+    <t>Ella Jones</t>
+  </si>
+  <si>
+    <t>Theo Hughes</t>
+  </si>
+  <si>
+    <t>2024-09-24</t>
+  </si>
+  <si>
+    <t>Grace Ahmed</t>
+  </si>
+  <si>
+    <t>Noah Chen</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Leo Hall</t>
+  </si>
+  <si>
+    <t>Jack Patel</t>
+  </si>
+  <si>
+    <t>Theo Wright</t>
+  </si>
+  <si>
+    <t>2024-09-17</t>
+  </si>
+  <si>
+    <t>Dev Ahmed</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>Leo Taylor</t>
+  </si>
+  <si>
+    <t>Dev Green</t>
+  </si>
+  <si>
+    <t>Grace Evans</t>
+  </si>
+  <si>
+    <t>16/09/2024</t>
+  </si>
+  <si>
+    <t>Quinn Hall</t>
+  </si>
+  <si>
+    <t>Max Khan</t>
+  </si>
+  <si>
+    <t>Sam Wright</t>
+  </si>
+  <si>
+    <t>23/09/2024</t>
+  </si>
+  <si>
+    <t>Ivy Walker</t>
+  </si>
+  <si>
+    <t>20 Sep 2024</t>
+  </si>
+  <si>
+    <t>Sam Patel</t>
+  </si>
+  <si>
+    <t>Lily Ahmed</t>
+  </si>
+  <si>
+    <t>Hari Wright</t>
+  </si>
+  <si>
+    <t>Priya Wilson</t>
+  </si>
+  <si>
+    <t>Isla Patel</t>
+  </si>
+  <si>
+    <t>Ben Brown</t>
+  </si>
+  <si>
+    <t>Lily Green</t>
+  </si>
+  <si>
+    <t>Max Jones</t>
+  </si>
+  <si>
+    <t>Priya Patel</t>
+  </si>
+  <si>
+    <t>Yusuf Patel</t>
+  </si>
+  <si>
+    <t>2024-09-16</t>
+  </si>
+  <si>
+    <t>Lily Brown</t>
+  </si>
+  <si>
+    <t>Yusuf Green</t>
+  </si>
+  <si>
+    <t>Priya Wright</t>
+  </si>
+  <si>
+    <t>Dev Taylor</t>
+  </si>
+  <si>
+    <t>Finn Wilson</t>
+  </si>
+  <si>
+    <t>Uma Jones</t>
+  </si>
+  <si>
+    <t>Ella Walker</t>
+  </si>
+  <si>
+    <t>Dev Khan</t>
+  </si>
+  <si>
+    <t>Kai Khan</t>
+  </si>
+  <si>
+    <t>2024-12-02</t>
   </si>
   <si>
     <t>Winter Ball</t>
@@ -43,403 +331,1147 @@
     <t>Member</t>
   </si>
   <si>
-    <t>Chloe Khan</t>
+    <t>£30.00</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>Ella Smith</t>
+  </si>
+  <si>
+    <t>23 Nov 2024</t>
+  </si>
+  <si>
+    <t>Yusuf Wilson</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>Tom Hall</t>
+  </si>
+  <si>
+    <t>06/12/2024</t>
+  </si>
+  <si>
+    <t>Quinn Patel</t>
+  </si>
+  <si>
+    <t>4 Dec 2024</t>
+  </si>
+  <si>
+    <t>Priya Khan</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>Hari Evans</t>
+  </si>
+  <si>
+    <t>22/11/2024</t>
+  </si>
+  <si>
+    <t>Chloe Green</t>
+  </si>
+  <si>
+    <t>17 Nov 2024</t>
+  </si>
+  <si>
+    <t>Mia Green</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>Vik Wilson</t>
+  </si>
+  <si>
+    <t>02/12/2024</t>
+  </si>
+  <si>
+    <t>Ella Hughes</t>
+  </si>
+  <si>
+    <t>7 Dec 2024</t>
+  </si>
+  <si>
+    <t>Omar Khan</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>Ben Evans</t>
+  </si>
+  <si>
+    <t>23/11/2024</t>
+  </si>
+  <si>
+    <t>22 Nov 2024</t>
+  </si>
+  <si>
+    <t>Mia Walker</t>
+  </si>
+  <si>
+    <t>2024-11-30</t>
+  </si>
+  <si>
+    <t>Rosa Green</t>
+  </si>
+  <si>
+    <t>11/11/2024</t>
+  </si>
+  <si>
+    <t>Isla Chen</t>
+  </si>
+  <si>
+    <t>9 Dec 2024</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>Ava Wilson</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>Omar Hall</t>
+  </si>
+  <si>
+    <t>Quinn Taylor</t>
+  </si>
+  <si>
+    <t>2024-11-13</t>
+  </si>
+  <si>
+    <t>Finn Taylor</t>
+  </si>
+  <si>
+    <t>10/11/2024</t>
+  </si>
+  <si>
+    <t>Priya Evans</t>
+  </si>
+  <si>
+    <t>Noah Taylor</t>
+  </si>
+  <si>
+    <t>2024-12-08</t>
+  </si>
+  <si>
+    <t>Noah Khan</t>
+  </si>
+  <si>
+    <t>16/11/2024</t>
+  </si>
+  <si>
+    <t>Rosa Taylor</t>
+  </si>
+  <si>
+    <t>8 Dec 2024</t>
+  </si>
+  <si>
+    <t>Chloe Taylor</t>
+  </si>
+  <si>
+    <t>2024-11-29</t>
+  </si>
+  <si>
+    <t>Quinn Smith</t>
+  </si>
+  <si>
+    <t>05/12/2024</t>
+  </si>
+  <si>
+    <t>Yusuf Hughes</t>
+  </si>
+  <si>
+    <t>6 Nov 2024</t>
+  </si>
+  <si>
+    <t>Jack Wilson</t>
+  </si>
+  <si>
+    <t>Priya Walker</t>
+  </si>
+  <si>
+    <t>26/11/2024</t>
+  </si>
+  <si>
+    <t>Isla Khan</t>
+  </si>
+  <si>
+    <t>Jack Khan</t>
+  </si>
+  <si>
+    <t>2024-11-27</t>
+  </si>
+  <si>
+    <t>Wren Evans</t>
+  </si>
+  <si>
+    <t>30/11/2024</t>
+  </si>
+  <si>
+    <t>Mia Chen</t>
+  </si>
+  <si>
+    <t>25 Nov 2024</t>
+  </si>
+  <si>
+    <t>Rosa Hughes</t>
+  </si>
+  <si>
+    <t>Wren Jones</t>
+  </si>
+  <si>
+    <t>09/12/2024</t>
+  </si>
+  <si>
+    <t>Leo Wright</t>
+  </si>
+  <si>
+    <t>Leo Hughes</t>
+  </si>
+  <si>
+    <t>Priya Taylor</t>
+  </si>
+  <si>
+    <t>2 Nov 2024</t>
+  </si>
+  <si>
+    <t>Tom Patel</t>
+  </si>
+  <si>
+    <t>Wren Khan</t>
+  </si>
+  <si>
+    <t>08/12/2024</t>
+  </si>
+  <si>
+    <t>Non-member</t>
+  </si>
+  <si>
+    <t>Sam Ahmed</t>
+  </si>
+  <si>
+    <t>£36.00</t>
+  </si>
+  <si>
+    <t>3 Nov 2024</t>
+  </si>
+  <si>
+    <t>Zara Jones</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>Rosa Wilson</t>
+  </si>
+  <si>
+    <t>9 Nov 2024</t>
+  </si>
+  <si>
+    <t>Wren Chen</t>
+  </si>
+  <si>
+    <t>Mia Hall</t>
+  </si>
+  <si>
+    <t>Yusuf Walker</t>
+  </si>
+  <si>
+    <t>07/12/2024</t>
+  </si>
+  <si>
+    <t>Uma Ahmed</t>
+  </si>
+  <si>
+    <t>8 Nov 2024</t>
+  </si>
+  <si>
+    <t>Theo Patel</t>
+  </si>
+  <si>
+    <t>Sam Green</t>
+  </si>
+  <si>
+    <t>14/11/2024</t>
+  </si>
+  <si>
+    <t>Chloe Chen</t>
+  </si>
+  <si>
+    <t>Sam Taylor</t>
+  </si>
+  <si>
+    <t>Zara Patel</t>
+  </si>
+  <si>
+    <t>20/11/2024</t>
+  </si>
+  <si>
+    <t>Grace Hall</t>
+  </si>
+  <si>
+    <t>27 Nov 2024</t>
+  </si>
+  <si>
+    <t>Hari Khan</t>
+  </si>
+  <si>
+    <t>2024-11-04</t>
+  </si>
+  <si>
+    <t>Max Hughes</t>
+  </si>
+  <si>
+    <t>24/11/2024</t>
+  </si>
+  <si>
+    <t>Chloe Hughes</t>
+  </si>
+  <si>
+    <t>6 Feb 2025</t>
+  </si>
+  <si>
+    <t>Spring Tour</t>
+  </si>
+  <si>
+    <t>Ella Khan</t>
+  </si>
+  <si>
+    <t>£120.00</t>
+  </si>
+  <si>
+    <t>2025-02-14</t>
+  </si>
+  <si>
+    <t>Rosa Khan</t>
+  </si>
+  <si>
+    <t>20/02/2025</t>
+  </si>
+  <si>
+    <t>27 Feb 2025</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>Tom Jones</t>
+  </si>
+  <si>
+    <t>06/02/2025</t>
+  </si>
+  <si>
+    <t>Isla Hall</t>
+  </si>
+  <si>
+    <t>22 Feb 2025</t>
+  </si>
+  <si>
+    <t>2025-02-07</t>
+  </si>
+  <si>
+    <t>05/02/2025</t>
+  </si>
+  <si>
+    <t>Grace Patel</t>
+  </si>
+  <si>
+    <t>26 Feb 2025</t>
+  </si>
+  <si>
+    <t>Ben Chen</t>
+  </si>
+  <si>
+    <t>2025-02-11</t>
+  </si>
+  <si>
+    <t>27/02/2025</t>
+  </si>
+  <si>
+    <t>3 Feb 2025</t>
+  </si>
+  <si>
+    <t>Zara Green</t>
+  </si>
+  <si>
+    <t>2025-01-28</t>
+  </si>
+  <si>
+    <t>Grace Wright</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>Isla Walker</t>
+  </si>
+  <si>
+    <t>Finn Chen</t>
+  </si>
+  <si>
+    <t>24/01/2025</t>
+  </si>
+  <si>
+    <t>Dev Hughes</t>
+  </si>
+  <si>
+    <t>25 Jan 2025</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
+    <t>2025-10-23</t>
+  </si>
+  <si>
+    <t>2025-10-30</t>
+  </si>
+  <si>
+    <t>2025-11-06</t>
+  </si>
+  <si>
+    <t>2025-11-13</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2025-11-27</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>18 Sep 2025</t>
+  </si>
+  <si>
+    <t>Theo Taylor</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>Quinn Evans</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
+    <t>17 Sep 2025</t>
+  </si>
+  <si>
+    <t>Chloe Evans</t>
+  </si>
+  <si>
+    <t>20/09/2025</t>
+  </si>
+  <si>
+    <t>Yusuf Wright</t>
+  </si>
+  <si>
+    <t>23 Sep 2025</t>
+  </si>
+  <si>
+    <t>Zara Wright</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>Hari Green</t>
+  </si>
+  <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>Tom Walker</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>Grace Taylor</t>
+  </si>
+  <si>
+    <t>24 Sep 2025</t>
+  </si>
+  <si>
+    <t>Tom Smith</t>
+  </si>
+  <si>
+    <t>Lily Hall</t>
+  </si>
+  <si>
+    <t>21/09/2025</t>
+  </si>
+  <si>
+    <t>Ava Jones</t>
+  </si>
+  <si>
+    <t>22/09/2025</t>
+  </si>
+  <si>
+    <t>Finn Evans</t>
+  </si>
+  <si>
+    <t>22 Sep 2025</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>Tom Hughes</t>
+  </si>
+  <si>
+    <t>Quinn Chen</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>Nina Chen</t>
+  </si>
+  <si>
+    <t>Ben Hall</t>
+  </si>
+  <si>
+    <t>21 Sep 2025</t>
+  </si>
+  <si>
+    <t>Ella Green</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>Ben Khan</t>
+  </si>
+  <si>
+    <t>Kai Smith</t>
+  </si>
+  <si>
+    <t>24/09/2025</t>
+  </si>
+  <si>
+    <t>Chloe Hall</t>
+  </si>
+  <si>
+    <t>Tom Khan</t>
+  </si>
+  <si>
+    <t>Lily Wilson</t>
+  </si>
+  <si>
+    <t>Leo Chen</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>Quinn Wright</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>Max Ahmed</t>
+  </si>
+  <si>
+    <t>Noah Ahmed</t>
+  </si>
+  <si>
+    <t>Chloe Jones</t>
+  </si>
+  <si>
+    <t>Kai Walker</t>
+  </si>
+  <si>
+    <t>Sam Evans</t>
+  </si>
+  <si>
+    <t>Ivy Hall</t>
+  </si>
+  <si>
+    <t>Ella Wright</t>
+  </si>
+  <si>
+    <t>Tom Wilson</t>
+  </si>
+  <si>
+    <t>Quinn Jones</t>
+  </si>
+  <si>
+    <t>Isla Wilson</t>
+  </si>
+  <si>
+    <t>20 Sep 2025</t>
+  </si>
+  <si>
+    <t>Yusuf Jones</t>
+  </si>
+  <si>
+    <t>Priya Hall</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
   </si>
   <si>
     <t>£32.00</t>
   </si>
   <si>
-    <t>09/11/2025</t>
-  </si>
-  <si>
-    <t>Ella Smith</t>
-  </si>
-  <si>
-    <t>15/11/2025</t>
-  </si>
-  <si>
-    <t>Dev Wilson</t>
+    <t>6 Dec 2025</t>
+  </si>
+  <si>
+    <t>2025-12-07</t>
+  </si>
+  <si>
+    <t>Mia Khan</t>
+  </si>
+  <si>
+    <t>29/11/2025</t>
+  </si>
+  <si>
+    <t>18 Nov 2025</t>
+  </si>
+  <si>
+    <t>Quinn Green</t>
+  </si>
+  <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
+    <t>Quinn Ahmed</t>
+  </si>
+  <si>
+    <t>2025-11-15</t>
+  </si>
+  <si>
+    <t>Max Green</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>14 Nov 2025</t>
+  </si>
+  <si>
+    <t>Mia Jones</t>
+  </si>
+  <si>
+    <t>2025-11-22</t>
+  </si>
+  <si>
+    <t>Noah Wright</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>Kai Evans</t>
+  </si>
+  <si>
+    <t>21 Nov 2025</t>
+  </si>
+  <si>
+    <t>Noah Evans</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>Max Wright</t>
+  </si>
+  <si>
+    <t>16 Nov 2025</t>
+  </si>
+  <si>
+    <t>Jack Hughes</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>Ben Smith</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>Omar Hughes</t>
+  </si>
+  <si>
+    <t>Nina Ahmed</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>Priya Brown</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>Ben Jones</t>
+  </si>
+  <si>
+    <t>Zara Brown</t>
+  </si>
+  <si>
+    <t>2025-11-23</t>
+  </si>
+  <si>
+    <t>Sam Wilson</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>Mia Evans</t>
+  </si>
+  <si>
+    <t>27 Nov 2025</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>Lily Hughes</t>
+  </si>
+  <si>
+    <t>25 Nov 2025</t>
+  </si>
+  <si>
+    <t>Yusuf Taylor</t>
+  </si>
+  <si>
+    <t>2025-11-29</t>
+  </si>
+  <si>
+    <t>Max Walker</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>Mia Smith</t>
+  </si>
+  <si>
+    <t>5 Dec 2025</t>
+  </si>
+  <si>
+    <t>Grace Chen</t>
+  </si>
+  <si>
+    <t>2025-11-16</t>
+  </si>
+  <si>
+    <t>Omar Taylor</t>
+  </si>
+  <si>
+    <t>Nina Smith</t>
+  </si>
+  <si>
+    <t>1 Dec 2025</t>
+  </si>
+  <si>
+    <t>Isla Smith</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>Max Evans</t>
+  </si>
+  <si>
+    <t>21/11/2025</t>
+  </si>
+  <si>
+    <t>Mia Taylor</t>
+  </si>
+  <si>
+    <t>Omar Evans</t>
+  </si>
+  <si>
+    <t>08/11/2025</t>
+  </si>
+  <si>
+    <t>Noah Brown</t>
+  </si>
+  <si>
+    <t>8 Dec 2025</t>
+  </si>
+  <si>
+    <t>Ava Hughes</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>Yusuf Brown</t>
+  </si>
+  <si>
+    <t>30 Nov 2025</t>
+  </si>
+  <si>
+    <t>Yusuf Evans</t>
+  </si>
+  <si>
+    <t>24/11/2025</t>
+  </si>
+  <si>
+    <t>Nina Khan</t>
+  </si>
+  <si>
+    <t>13 Nov 2025</t>
+  </si>
+  <si>
+    <t>Ivy Ahmed</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>Tom Wright</t>
+  </si>
+  <si>
+    <t>Dev Jones</t>
+  </si>
+  <si>
+    <t>Leo Jones</t>
+  </si>
+  <si>
+    <t>Sam Hall</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>Omar Wright</t>
+  </si>
+  <si>
+    <t>12 Nov 2025</t>
+  </si>
+  <si>
+    <t>Ava Taylor</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
   </si>
   <si>
     <t>05/11/2025</t>
   </si>
   <si>
-    <t>Vik Brown</t>
-  </si>
-  <si>
-    <t>11/11/2025</t>
-  </si>
-  <si>
-    <t>Omar Taylor</t>
-  </si>
-  <si>
-    <t>04/11/2025</t>
+    <t>Theo Smith</t>
+  </si>
+  <si>
+    <t>Noah Smith</t>
+  </si>
+  <si>
+    <t>2025-11-17</t>
+  </si>
+  <si>
+    <t>Nina Walker</t>
+  </si>
+  <si>
+    <t>£40.00</t>
+  </si>
+  <si>
+    <t>Ava Evans</t>
+  </si>
+  <si>
+    <t>Kai Jones</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>Ben Taylor</t>
+  </si>
+  <si>
+    <t>Ivy Brown</t>
+  </si>
+  <si>
+    <t>22 Nov 2025</t>
+  </si>
+  <si>
+    <t>Uma Walker</t>
+  </si>
+  <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
+    <t>17 Nov 2025</t>
+  </si>
+  <si>
+    <t>Sam Brown</t>
+  </si>
+  <si>
+    <t>Chloe Smith</t>
+  </si>
+  <si>
+    <t>2025-12-06</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>20 Nov 2025</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>Hari Jones</t>
+  </si>
+  <si>
+    <t>26 Nov 2025</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>Finn Hughes</t>
+  </si>
+  <si>
+    <t>Nina Hall</t>
+  </si>
+  <si>
+    <t>Omar Chen</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>Kai Taylor</t>
+  </si>
+  <si>
+    <t>18 Feb 2026</t>
+  </si>
+  <si>
+    <t>Quinn Khan</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>26 Feb 2026</t>
+  </si>
+  <si>
+    <t>Quinn Hughes</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>Sam Jones</t>
+  </si>
+  <si>
+    <t>Ella Evans</t>
+  </si>
+  <si>
+    <t>27 Feb 2026</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>01/02/2026</t>
+  </si>
+  <si>
+    <t>31 Jan 2026</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>21/02/2026</t>
+  </si>
+  <si>
+    <t>Jack Taylor</t>
+  </si>
+  <si>
+    <t>7 Feb 2026</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>Charity Quiz</t>
+  </si>
+  <si>
+    <t>Team ticket</t>
+  </si>
+  <si>
+    <t>£4.00</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>Sam Chen</t>
+  </si>
+  <si>
+    <t>12 Feb 2026</t>
+  </si>
+  <si>
+    <t>Omar Brown</t>
+  </si>
+  <si>
+    <t>Mia Ahmed</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>Uma Evans</t>
+  </si>
+  <si>
+    <t>2026-02-15</t>
+  </si>
+  <si>
+    <t>Chloe Patel</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>14 Feb 2026</t>
+  </si>
+  <si>
+    <t>2026-02-09</t>
+  </si>
+  <si>
+    <t>Rosa Hall</t>
+  </si>
+  <si>
+    <t>17 Feb 2026</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>Hari Ahmed</t>
+  </si>
+  <si>
+    <t>8 Feb 2026</t>
+  </si>
+  <si>
+    <t>08/02/2026</t>
+  </si>
+  <si>
+    <t>17/02/2026</t>
+  </si>
+  <si>
+    <t>Leo Patel</t>
+  </si>
+  <si>
+    <t>2026-02-08</t>
+  </si>
+  <si>
+    <t>Ivy Evans</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>16 Feb 2026</t>
+  </si>
+  <si>
+    <t>2026-02-11</t>
+  </si>
+  <si>
+    <t>Nina Evans</t>
+  </si>
+  <si>
+    <t>13 Feb 2026</t>
+  </si>
+  <si>
+    <t>Uma Brown</t>
+  </si>
+  <si>
+    <t>Finn Walker</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>11 Feb 2026</t>
+  </si>
+  <si>
+    <t>Wren Taylor</t>
   </si>
   <si>
     <t>Ella Brown</t>
   </si>
   <si>
-    <t>Yusuf Khan</t>
-  </si>
-  <si>
-    <t>Kai Evans</t>
-  </si>
-  <si>
-    <t>Jack Chen</t>
-  </si>
-  <si>
-    <t>17/11/2025</t>
-  </si>
-  <si>
-    <t>Chloe Ahmed</t>
-  </si>
-  <si>
-    <t>Kai Smith</t>
-  </si>
-  <si>
-    <t>Chloe Walker</t>
-  </si>
-  <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
-    <t>Omar Wright</t>
-  </si>
-  <si>
-    <t>Priya Patel</t>
-  </si>
-  <si>
-    <t>24/11/2025</t>
-  </si>
-  <si>
-    <t>Priya Smith</t>
-  </si>
-  <si>
-    <t>Wren Ahmed</t>
-  </si>
-  <si>
-    <t>Priya Evans</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
-  </si>
-  <si>
-    <t>Rosa Evans</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>Ava Patel</t>
-  </si>
-  <si>
-    <t>23/11/2025</t>
-  </si>
-  <si>
-    <t>Sam Khan</t>
-  </si>
-  <si>
-    <t>Kai Patel</t>
-  </si>
-  <si>
-    <t>Uma Ahmed</t>
-  </si>
-  <si>
-    <t>Yusuf Taylor</t>
-  </si>
-  <si>
-    <t>Sam Patel</t>
-  </si>
-  <si>
-    <t>08/11/2025</t>
-  </si>
-  <si>
-    <t>Vik Jones</t>
-  </si>
-  <si>
-    <t>21/11/2025</t>
-  </si>
-  <si>
-    <t>Hari Smith</t>
-  </si>
-  <si>
-    <t>10/11/2025</t>
-  </si>
-  <si>
-    <t>Dev Jones</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>Sam Jones</t>
-  </si>
-  <si>
-    <t>Ava Taylor</t>
-  </si>
-  <si>
-    <t>Tom Brown</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>Uma Wright</t>
-  </si>
-  <si>
-    <t>19/11/2025</t>
-  </si>
-  <si>
-    <t>Hari Taylor</t>
-  </si>
-  <si>
-    <t>02/11/2025</t>
-  </si>
-  <si>
-    <t>Wren Patel</t>
-  </si>
-  <si>
-    <t>Non-member</t>
-  </si>
-  <si>
-    <t>Kai Walker</t>
-  </si>
-  <si>
-    <t>£40.00</t>
-  </si>
-  <si>
-    <t>01/11/2025</t>
-  </si>
-  <si>
-    <t>Finn Smith</t>
-  </si>
-  <si>
-    <t>Yusuf Wilson</t>
-  </si>
-  <si>
-    <t>Ben Walker</t>
-  </si>
-  <si>
-    <t>Quinn Evans</t>
-  </si>
-  <si>
-    <t>Quinn Taylor</t>
-  </si>
-  <si>
-    <t>Omar Jones</t>
-  </si>
-  <si>
-    <t>Wren Wilson</t>
-  </si>
-  <si>
-    <t>Wren Khan</t>
-  </si>
-  <si>
-    <t>Ava Ahmed</t>
-  </si>
-  <si>
-    <t>22/11/2025</t>
-  </si>
-  <si>
-    <t>Yusuf Walker</t>
-  </si>
-  <si>
-    <t>12/11/2025</t>
-  </si>
-  <si>
-    <t>Vik Taylor</t>
-  </si>
-  <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t>Chloe Patel</t>
-  </si>
-  <si>
-    <t>Isla Smith</t>
-  </si>
-  <si>
-    <t>03/09/2025</t>
-  </si>
-  <si>
-    <t>Freshers Social</t>
-  </si>
-  <si>
-    <t>Entry</t>
-  </si>
-  <si>
-    <t>Grace Patel</t>
-  </si>
-  <si>
-    <t>£5.00</t>
-  </si>
-  <si>
-    <t>21/09/2025</t>
-  </si>
-  <si>
-    <t>Ella Wilson</t>
-  </si>
-  <si>
-    <t>13/09/2025</t>
-  </si>
-  <si>
-    <t>Jack Wright</t>
-  </si>
-  <si>
-    <t>18/09/2025</t>
-  </si>
-  <si>
-    <t>Quinn Brown</t>
-  </si>
-  <si>
-    <t>09/09/2025</t>
-  </si>
-  <si>
-    <t>Kai Jones</t>
-  </si>
-  <si>
-    <t>07/09/2025</t>
-  </si>
-  <si>
-    <t>Zara Khan</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>Zara Smith</t>
-  </si>
-  <si>
-    <t>15/09/2025</t>
-  </si>
-  <si>
-    <t>Ella Khan</t>
-  </si>
-  <si>
-    <t>Priya Brown</t>
-  </si>
-  <si>
-    <t>Finn Ahmed</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>17/09/2025</t>
-  </si>
-  <si>
-    <t>Dev Patel</t>
-  </si>
-  <si>
-    <t>Ava Brown</t>
-  </si>
-  <si>
-    <t>Chloe Jones</t>
-  </si>
-  <si>
-    <t>06/09/2025</t>
-  </si>
-  <si>
-    <t>Grace Ahmed</t>
-  </si>
-  <si>
-    <t>22/09/2025</t>
-  </si>
-  <si>
-    <t>Ben Jones</t>
-  </si>
-  <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>Isla Taylor</t>
-  </si>
-  <si>
-    <t>24/09/2025</t>
-  </si>
-  <si>
-    <t>Zara Wilson</t>
-  </si>
-  <si>
-    <t>08/09/2025</t>
-  </si>
-  <si>
-    <t>Zara Chen</t>
-  </si>
-  <si>
-    <t>Max Evans</t>
-  </si>
-  <si>
-    <t>20/09/2025</t>
-  </si>
-  <si>
-    <t>Sam Smith</t>
-  </si>
-  <si>
-    <t>Nina Taylor</t>
-  </si>
-  <si>
-    <t>Rosa Ahmed</t>
-  </si>
-  <si>
-    <t>14/09/2025</t>
-  </si>
-  <si>
-    <t>Ella Evans</t>
-  </si>
-  <si>
-    <t>Jack Evans</t>
-  </si>
-  <si>
-    <t>04/09/2025</t>
-  </si>
-  <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
-    <t>Lily Khan</t>
-  </si>
-  <si>
-    <t>Lily Walker</t>
-  </si>
-  <si>
-    <t>Priya Khan</t>
-  </si>
-  <si>
-    <t>Tom Patel</t>
-  </si>
-  <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
-    <t>Dev Taylor</t>
-  </si>
-  <si>
-    <t>Lily Chen</t>
-  </si>
-  <si>
-    <t>10/09/2025</t>
-  </si>
-  <si>
-    <t>Jack Taylor</t>
-  </si>
-  <si>
-    <t>Isla Chen</t>
-  </si>
-  <si>
-    <t>Lily Brown</t>
-  </si>
-  <si>
-    <t>Ben Khan</t>
-  </si>
-  <si>
-    <t>Finn Wilson</t>
-  </si>
-  <si>
-    <t>Omar Patel</t>
+    <t>10 Feb 2026</t>
+  </si>
+  <si>
+    <t>Finn Green</t>
+  </si>
+  <si>
+    <t>14/02/2026</t>
+  </si>
+  <si>
+    <t>Ava Wright</t>
+  </si>
+  <si>
+    <t>Omar Walker</t>
+  </si>
+  <si>
+    <t>Wren Green</t>
   </si>
 </sst>
 </file>
@@ -816,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G371"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
@@ -862,7 +1894,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -876,18 +1908,18 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -896,18 +1928,18 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -916,18 +1948,18 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -936,18 +1968,18 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -956,18 +1988,18 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -976,18 +2008,18 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -996,18 +2028,18 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -1016,18 +2048,18 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -1036,18 +2068,18 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -1056,18 +2088,18 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -1076,18 +2108,18 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -1096,18 +2128,18 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -1116,18 +2148,18 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -1136,18 +2168,18 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -1156,18 +2188,18 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -1176,18 +2208,18 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -1196,18 +2228,18 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -1216,18 +2248,18 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -1236,50 +2268,50 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -1287,59 +2319,59 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -1347,79 +2379,79 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F30">
         <v>2</v>
@@ -1427,59 +2459,59 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1487,42 +2519,42 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1530,19 +2562,19 @@
         <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
         <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1550,36 +2582,36 @@
         <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
         <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" t="s">
         <v>62</v>
       </c>
-      <c r="D38" t="s">
-        <v>63</v>
-      </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F38">
         <v>2</v>
@@ -1587,19 +2619,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -1607,59 +2639,59 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E42" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1667,19 +2699,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E43" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -1687,119 +2719,119 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E44" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -1807,19 +2839,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E50" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -1827,39 +2859,39 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E51" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E52" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F52">
         <v>2</v>
@@ -1867,19 +2899,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F53">
         <v>2</v>
@@ -1887,59 +2919,59 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E54" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s">
         <v>85</v>
       </c>
       <c r="E55" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E56" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -1947,59 +2979,59 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E57" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D58" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E58" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C59" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D59" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E59" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F59">
         <v>2</v>
@@ -2007,159 +3039,159 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E60" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D61" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E61" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E62" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D63" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E63" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E64" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E65" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D66" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E66" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E67" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2167,119 +3199,119 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B68" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" t="s">
         <v>99</v>
       </c>
-      <c r="B68" t="s">
-        <v>83</v>
-      </c>
-      <c r="C68" t="s">
-        <v>84</v>
-      </c>
-      <c r="D68" t="s">
-        <v>107</v>
-      </c>
       <c r="E68" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E69" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D70" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E70" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D71" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="E71" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s">
+        <v>105</v>
+      </c>
+      <c r="D72" t="s">
         <v>84</v>
       </c>
-      <c r="D72" t="s">
-        <v>114</v>
-      </c>
       <c r="E72" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C73" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D73" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E73" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -2287,19 +3319,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="E74" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F74">
         <v>2</v>
@@ -2307,39 +3339,39 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C75" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E75" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C76" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2347,19 +3379,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C77" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D77" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E77" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -2367,19 +3399,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D78" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E78" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F78">
         <v>2</v>
@@ -2387,119 +3419,119 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E79" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D80" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E80" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E81" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="E82" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F82">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>127</v>
+      </c>
+      <c r="B83" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83" t="s">
+        <v>105</v>
+      </c>
+      <c r="D83" t="s">
         <v>128</v>
       </c>
-      <c r="B83" t="s">
-        <v>83</v>
-      </c>
-      <c r="C83" t="s">
-        <v>84</v>
-      </c>
-      <c r="D83" t="s">
-        <v>129</v>
-      </c>
       <c r="E83" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F83">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D84" t="s">
         <v>130</v>
       </c>
       <c r="E84" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -2507,19 +3539,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D85" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E85" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F85">
         <v>2</v>
@@ -2527,19 +3559,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C86" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D86" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E86" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -2547,79 +3579,79 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B87" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C87" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D87" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E87" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B88" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C88" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D88" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="E88" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B89" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="E89" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="B90" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C90" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E90" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F90">
         <v>2</v>
@@ -2627,99 +3659,99 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="B91" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="E91" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F91">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D92" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E92" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="B93" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C93" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E93" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F93">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C94" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D94" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E94" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C95" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D95" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E95" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F95">
         <v>2</v>
@@ -2727,39 +3759,39 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="B96" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C96" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D96" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E96" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F96">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="B97" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C97" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D97" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E97" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -2767,22 +3799,5482 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>153</v>
+      </c>
+      <c r="B98" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98" t="s">
+        <v>105</v>
+      </c>
+      <c r="D98" t="s">
+        <v>154</v>
+      </c>
+      <c r="E98" t="s">
+        <v>106</v>
+      </c>
+      <c r="F98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>155</v>
+      </c>
+      <c r="B99" t="s">
+        <v>104</v>
+      </c>
+      <c r="C99" t="s">
+        <v>105</v>
+      </c>
+      <c r="D99" t="s">
+        <v>156</v>
+      </c>
+      <c r="E99" t="s">
+        <v>106</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>157</v>
+      </c>
+      <c r="B100" t="s">
+        <v>104</v>
+      </c>
+      <c r="C100" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" t="s">
+        <v>158</v>
+      </c>
+      <c r="E100" t="s">
+        <v>106</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>159</v>
+      </c>
+      <c r="B101" t="s">
+        <v>104</v>
+      </c>
+      <c r="C101" t="s">
+        <v>105</v>
+      </c>
+      <c r="D101" t="s">
+        <v>160</v>
+      </c>
+      <c r="E101" t="s">
+        <v>106</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>155</v>
+      </c>
+      <c r="B102" t="s">
+        <v>104</v>
+      </c>
+      <c r="C102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102" t="s">
+        <v>161</v>
+      </c>
+      <c r="E102" t="s">
+        <v>106</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>162</v>
+      </c>
+      <c r="B103" t="s">
+        <v>104</v>
+      </c>
+      <c r="C103" t="s">
+        <v>105</v>
+      </c>
+      <c r="D103" t="s">
+        <v>163</v>
+      </c>
+      <c r="E103" t="s">
+        <v>106</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>153</v>
+      </c>
+      <c r="B104" t="s">
+        <v>104</v>
+      </c>
+      <c r="C104" t="s">
+        <v>105</v>
+      </c>
+      <c r="D104" t="s">
+        <v>164</v>
+      </c>
+      <c r="E104" t="s">
+        <v>106</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>165</v>
+      </c>
+      <c r="B105" t="s">
+        <v>104</v>
+      </c>
+      <c r="C105" t="s">
+        <v>105</v>
+      </c>
+      <c r="D105" t="s">
+        <v>166</v>
+      </c>
+      <c r="E105" t="s">
+        <v>106</v>
+      </c>
+      <c r="F105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>167</v>
+      </c>
+      <c r="B106" t="s">
+        <v>104</v>
+      </c>
+      <c r="C106" t="s">
+        <v>105</v>
+      </c>
+      <c r="D106" t="s">
+        <v>168</v>
+      </c>
+      <c r="E106" t="s">
+        <v>106</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>169</v>
+      </c>
+      <c r="B107" t="s">
+        <v>104</v>
+      </c>
+      <c r="C107" t="s">
+        <v>105</v>
+      </c>
+      <c r="D107" t="s">
+        <v>170</v>
+      </c>
+      <c r="E107" t="s">
+        <v>106</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>103</v>
+      </c>
+      <c r="B108" t="s">
+        <v>104</v>
+      </c>
+      <c r="C108" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" t="s">
+        <v>171</v>
+      </c>
+      <c r="E108" t="s">
+        <v>106</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>172</v>
+      </c>
+      <c r="B109" t="s">
+        <v>104</v>
+      </c>
+      <c r="C109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" t="s">
+        <v>173</v>
+      </c>
+      <c r="E109" t="s">
+        <v>106</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>159</v>
+      </c>
+      <c r="B110" t="s">
+        <v>104</v>
+      </c>
+      <c r="C110" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" t="s">
+        <v>88</v>
+      </c>
+      <c r="E110" t="s">
+        <v>106</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>155</v>
+      </c>
+      <c r="B111" t="s">
+        <v>104</v>
+      </c>
+      <c r="C111" t="s">
+        <v>105</v>
+      </c>
+      <c r="D111" t="s">
+        <v>174</v>
+      </c>
+      <c r="E111" t="s">
+        <v>106</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>172</v>
+      </c>
+      <c r="B112" t="s">
+        <v>104</v>
+      </c>
+      <c r="C112" t="s">
+        <v>105</v>
+      </c>
+      <c r="D112" t="s">
+        <v>175</v>
+      </c>
+      <c r="E112" t="s">
+        <v>106</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>176</v>
+      </c>
+      <c r="B113" t="s">
+        <v>104</v>
+      </c>
+      <c r="C113" t="s">
+        <v>105</v>
+      </c>
+      <c r="D113" t="s">
+        <v>177</v>
+      </c>
+      <c r="E113" t="s">
+        <v>106</v>
+      </c>
+      <c r="F113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" t="s">
+        <v>104</v>
+      </c>
+      <c r="C114" t="s">
+        <v>105</v>
+      </c>
+      <c r="D114" t="s">
+        <v>178</v>
+      </c>
+      <c r="E114" t="s">
+        <v>106</v>
+      </c>
+      <c r="F114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>179</v>
+      </c>
+      <c r="B115" t="s">
+        <v>104</v>
+      </c>
+      <c r="C115" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115" t="s">
+        <v>181</v>
+      </c>
+      <c r="E115" t="s">
+        <v>182</v>
+      </c>
+      <c r="F115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>183</v>
+      </c>
+      <c r="B116" t="s">
+        <v>104</v>
+      </c>
+      <c r="C116" t="s">
+        <v>180</v>
+      </c>
+      <c r="D116" t="s">
+        <v>184</v>
+      </c>
+      <c r="E116" t="s">
+        <v>182</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>185</v>
+      </c>
+      <c r="B117" t="s">
+        <v>104</v>
+      </c>
+      <c r="C117" t="s">
+        <v>180</v>
+      </c>
+      <c r="D117" t="s">
+        <v>186</v>
+      </c>
+      <c r="E117" t="s">
+        <v>182</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>179</v>
+      </c>
+      <c r="B118" t="s">
+        <v>104</v>
+      </c>
+      <c r="C118" t="s">
+        <v>180</v>
+      </c>
+      <c r="D118" t="s">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
-        <v>83</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="E118" t="s">
+        <v>182</v>
+      </c>
+      <c r="F118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>187</v>
+      </c>
+      <c r="B119" t="s">
+        <v>104</v>
+      </c>
+      <c r="C119" t="s">
+        <v>180</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" t="s">
+        <v>182</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>134</v>
+      </c>
+      <c r="B120" t="s">
+        <v>104</v>
+      </c>
+      <c r="C120" t="s">
+        <v>180</v>
+      </c>
+      <c r="D120" t="s">
+        <v>188</v>
+      </c>
+      <c r="E120" t="s">
+        <v>182</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121" t="s">
+        <v>104</v>
+      </c>
+      <c r="C121" t="s">
+        <v>180</v>
+      </c>
+      <c r="D121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E121" t="s">
+        <v>182</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>138</v>
+      </c>
+      <c r="B122" t="s">
+        <v>104</v>
+      </c>
+      <c r="C122" t="s">
+        <v>180</v>
+      </c>
+      <c r="D122" t="s">
+        <v>189</v>
+      </c>
+      <c r="E122" t="s">
+        <v>182</v>
+      </c>
+      <c r="F122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>111</v>
+      </c>
+      <c r="B123" t="s">
+        <v>104</v>
+      </c>
+      <c r="C123" t="s">
+        <v>180</v>
+      </c>
+      <c r="D123" t="s">
+        <v>190</v>
+      </c>
+      <c r="E123" t="s">
+        <v>182</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>191</v>
+      </c>
+      <c r="B124" t="s">
+        <v>104</v>
+      </c>
+      <c r="C124" t="s">
+        <v>180</v>
+      </c>
+      <c r="D124" t="s">
+        <v>192</v>
+      </c>
+      <c r="E124" t="s">
+        <v>182</v>
+      </c>
+      <c r="F124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>193</v>
+      </c>
+      <c r="B125" t="s">
+        <v>104</v>
+      </c>
+      <c r="C125" t="s">
+        <v>180</v>
+      </c>
+      <c r="D125" t="s">
+        <v>194</v>
+      </c>
+      <c r="E125" t="s">
+        <v>182</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>185</v>
+      </c>
+      <c r="B126" t="s">
+        <v>104</v>
+      </c>
+      <c r="C126" t="s">
+        <v>180</v>
+      </c>
+      <c r="D126" t="s">
+        <v>195</v>
+      </c>
+      <c r="E126" t="s">
+        <v>182</v>
+      </c>
+      <c r="F126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>196</v>
+      </c>
+      <c r="B127" t="s">
+        <v>104</v>
+      </c>
+      <c r="C127" t="s">
+        <v>180</v>
+      </c>
+      <c r="D127" t="s">
+        <v>197</v>
+      </c>
+      <c r="E127" t="s">
+        <v>182</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" t="s">
+        <v>180</v>
+      </c>
+      <c r="D128" t="s">
+        <v>198</v>
+      </c>
+      <c r="E128" t="s">
+        <v>182</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>111</v>
+      </c>
+      <c r="B129" t="s">
+        <v>104</v>
+      </c>
+      <c r="C129" t="s">
+        <v>180</v>
+      </c>
+      <c r="D129" t="s">
+        <v>199</v>
+      </c>
+      <c r="E129" t="s">
+        <v>182</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>200</v>
+      </c>
+      <c r="B130" t="s">
+        <v>104</v>
+      </c>
+      <c r="C130" t="s">
+        <v>180</v>
+      </c>
+      <c r="D130" t="s">
+        <v>201</v>
+      </c>
+      <c r="E130" t="s">
+        <v>182</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>202</v>
+      </c>
+      <c r="B131" t="s">
+        <v>104</v>
+      </c>
+      <c r="C131" t="s">
+        <v>180</v>
+      </c>
+      <c r="D131" t="s">
+        <v>203</v>
+      </c>
+      <c r="E131" t="s">
+        <v>182</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>204</v>
+      </c>
+      <c r="B132" t="s">
+        <v>104</v>
+      </c>
+      <c r="C132" t="s">
+        <v>180</v>
+      </c>
+      <c r="D132" t="s">
+        <v>205</v>
+      </c>
+      <c r="E132" t="s">
+        <v>182</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>206</v>
+      </c>
+      <c r="B133" t="s">
+        <v>104</v>
+      </c>
+      <c r="C133" t="s">
+        <v>180</v>
+      </c>
+      <c r="D133" t="s">
+        <v>207</v>
+      </c>
+      <c r="E133" t="s">
+        <v>182</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>208</v>
+      </c>
+      <c r="B134" t="s">
+        <v>209</v>
+      </c>
+      <c r="C134" t="s">
+        <v>105</v>
+      </c>
+      <c r="D134" t="s">
+        <v>210</v>
+      </c>
+      <c r="E134" t="s">
+        <v>211</v>
+      </c>
+      <c r="F134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>212</v>
+      </c>
+      <c r="B135" t="s">
+        <v>209</v>
+      </c>
+      <c r="C135" t="s">
+        <v>105</v>
+      </c>
+      <c r="D135" t="s">
+        <v>213</v>
+      </c>
+      <c r="E135" t="s">
+        <v>211</v>
+      </c>
+      <c r="F135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>214</v>
+      </c>
+      <c r="B136" t="s">
+        <v>209</v>
+      </c>
+      <c r="C136" t="s">
+        <v>105</v>
+      </c>
+      <c r="D136" t="s">
+        <v>197</v>
+      </c>
+      <c r="E136" t="s">
+        <v>211</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>215</v>
+      </c>
+      <c r="B137" t="s">
+        <v>209</v>
+      </c>
+      <c r="C137" t="s">
+        <v>105</v>
+      </c>
+      <c r="D137" t="s">
+        <v>198</v>
+      </c>
+      <c r="E137" t="s">
+        <v>211</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>216</v>
+      </c>
+      <c r="B138" t="s">
+        <v>209</v>
+      </c>
+      <c r="C138" t="s">
+        <v>105</v>
+      </c>
+      <c r="D138" t="s">
+        <v>217</v>
+      </c>
+      <c r="E138" t="s">
+        <v>211</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>218</v>
+      </c>
+      <c r="B139" t="s">
+        <v>209</v>
+      </c>
+      <c r="C139" t="s">
+        <v>105</v>
+      </c>
+      <c r="D139" t="s">
+        <v>219</v>
+      </c>
+      <c r="E139" t="s">
+        <v>211</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>220</v>
+      </c>
+      <c r="B140" t="s">
+        <v>209</v>
+      </c>
+      <c r="C140" t="s">
+        <v>105</v>
+      </c>
+      <c r="D140" t="s">
+        <v>43</v>
+      </c>
+      <c r="E140" t="s">
+        <v>211</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>221</v>
+      </c>
+      <c r="B141" t="s">
+        <v>209</v>
+      </c>
+      <c r="C141" t="s">
+        <v>105</v>
+      </c>
+      <c r="D141" t="s">
+        <v>128</v>
+      </c>
+      <c r="E141" t="s">
+        <v>211</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>222</v>
+      </c>
+      <c r="B142" t="s">
+        <v>209</v>
+      </c>
+      <c r="C142" t="s">
+        <v>105</v>
+      </c>
+      <c r="D142" t="s">
+        <v>223</v>
+      </c>
+      <c r="E142" t="s">
+        <v>211</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>224</v>
+      </c>
+      <c r="B143" t="s">
+        <v>209</v>
+      </c>
+      <c r="C143" t="s">
+        <v>105</v>
+      </c>
+      <c r="D143" t="s">
+        <v>225</v>
+      </c>
+      <c r="E143" t="s">
+        <v>211</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>226</v>
+      </c>
+      <c r="B144" t="s">
+        <v>209</v>
+      </c>
+      <c r="C144" t="s">
+        <v>105</v>
+      </c>
+      <c r="D144" t="s">
+        <v>49</v>
+      </c>
+      <c r="E144" t="s">
+        <v>211</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>227</v>
+      </c>
+      <c r="B145" t="s">
+        <v>209</v>
+      </c>
+      <c r="C145" t="s">
+        <v>105</v>
+      </c>
+      <c r="D145" t="s">
+        <v>75</v>
+      </c>
+      <c r="E145" t="s">
+        <v>211</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>228</v>
+      </c>
+      <c r="B146" t="s">
+        <v>209</v>
+      </c>
+      <c r="C146" t="s">
+        <v>105</v>
+      </c>
+      <c r="D146" t="s">
+        <v>229</v>
+      </c>
+      <c r="E146" t="s">
+        <v>211</v>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>230</v>
+      </c>
+      <c r="B147" t="s">
+        <v>209</v>
+      </c>
+      <c r="C147" t="s">
+        <v>105</v>
+      </c>
+      <c r="D147" t="s">
+        <v>231</v>
+      </c>
+      <c r="E147" t="s">
+        <v>211</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>232</v>
+      </c>
+      <c r="B148" t="s">
+        <v>209</v>
+      </c>
+      <c r="C148" t="s">
+        <v>105</v>
+      </c>
+      <c r="D148" t="s">
+        <v>57</v>
+      </c>
+      <c r="E148" t="s">
+        <v>211</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>215</v>
+      </c>
+      <c r="B149" t="s">
+        <v>209</v>
+      </c>
+      <c r="C149" t="s">
+        <v>105</v>
+      </c>
+      <c r="D149" t="s">
+        <v>233</v>
+      </c>
+      <c r="E149" t="s">
+        <v>211</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>216</v>
+      </c>
+      <c r="B150" t="s">
+        <v>209</v>
+      </c>
+      <c r="C150" t="s">
+        <v>105</v>
+      </c>
+      <c r="D150" t="s">
+        <v>234</v>
+      </c>
+      <c r="E150" t="s">
+        <v>211</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>235</v>
+      </c>
+      <c r="B151" t="s">
+        <v>209</v>
+      </c>
+      <c r="C151" t="s">
+        <v>105</v>
+      </c>
+      <c r="D151" t="s">
+        <v>236</v>
+      </c>
+      <c r="E151" t="s">
+        <v>211</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>237</v>
+      </c>
+      <c r="B152" t="s">
+        <v>209</v>
+      </c>
+      <c r="C152" t="s">
+        <v>105</v>
+      </c>
+      <c r="D152" t="s">
+        <v>61</v>
+      </c>
+      <c r="E152" t="s">
+        <v>211</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>238</v>
+      </c>
+      <c r="B153" t="s">
+        <v>8</v>
+      </c>
+      <c r="C153" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>239</v>
+      </c>
+      <c r="B154" t="s">
+        <v>8</v>
+      </c>
+      <c r="C154" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>240</v>
+      </c>
+      <c r="B155" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>241</v>
+      </c>
+      <c r="B156" t="s">
+        <v>8</v>
+      </c>
+      <c r="C156" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>242</v>
+      </c>
+      <c r="B157" t="s">
+        <v>8</v>
+      </c>
+      <c r="C157" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>243</v>
+      </c>
+      <c r="B158" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>244</v>
+      </c>
+      <c r="B159" t="s">
+        <v>8</v>
+      </c>
+      <c r="C159" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>245</v>
+      </c>
+      <c r="B160" t="s">
+        <v>8</v>
+      </c>
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>246</v>
+      </c>
+      <c r="B161" t="s">
+        <v>8</v>
+      </c>
+      <c r="C161" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>247</v>
+      </c>
+      <c r="B162" t="s">
+        <v>8</v>
+      </c>
+      <c r="C162" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>248</v>
+      </c>
+      <c r="B163" t="s">
+        <v>8</v>
+      </c>
+      <c r="C163" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" t="s">
+        <v>10</v>
+      </c>
+      <c r="E163" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>249</v>
+      </c>
+      <c r="B164" t="s">
+        <v>8</v>
+      </c>
+      <c r="C164" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>250</v>
+      </c>
+      <c r="B165" t="s">
+        <v>8</v>
+      </c>
+      <c r="C165" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>251</v>
+      </c>
+      <c r="B166" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>252</v>
+      </c>
+      <c r="B167" t="s">
+        <v>8</v>
+      </c>
+      <c r="C167" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>253</v>
+      </c>
+      <c r="B168" t="s">
+        <v>8</v>
+      </c>
+      <c r="C168" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>254</v>
+      </c>
+      <c r="B169" t="s">
+        <v>8</v>
+      </c>
+      <c r="C169" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" t="s">
+        <v>10</v>
+      </c>
+      <c r="E169" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>255</v>
+      </c>
+      <c r="B170" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>256</v>
+      </c>
+      <c r="B171" t="s">
+        <v>8</v>
+      </c>
+      <c r="C171" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" t="s">
+        <v>10</v>
+      </c>
+      <c r="E171" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>257</v>
+      </c>
+      <c r="B172" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" t="s">
+        <v>10</v>
+      </c>
+      <c r="E172" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>258</v>
+      </c>
+      <c r="B173" t="s">
+        <v>32</v>
+      </c>
+      <c r="C173" t="s">
+        <v>33</v>
+      </c>
+      <c r="D173" t="s">
+        <v>259</v>
+      </c>
+      <c r="E173" t="s">
+        <v>35</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>260</v>
+      </c>
+      <c r="B174" t="s">
+        <v>32</v>
+      </c>
+      <c r="C174" t="s">
+        <v>33</v>
+      </c>
+      <c r="D174" t="s">
+        <v>261</v>
+      </c>
+      <c r="E174" t="s">
+        <v>35</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>262</v>
+      </c>
+      <c r="B175" t="s">
+        <v>32</v>
+      </c>
+      <c r="C175" t="s">
+        <v>33</v>
+      </c>
+      <c r="D175" t="s">
+        <v>39</v>
+      </c>
+      <c r="E175" t="s">
+        <v>35</v>
+      </c>
+      <c r="F175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>263</v>
+      </c>
+      <c r="B176" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176" t="s">
+        <v>33</v>
+      </c>
+      <c r="D176" t="s">
+        <v>219</v>
+      </c>
+      <c r="E176" t="s">
+        <v>35</v>
+      </c>
+      <c r="F176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>260</v>
+      </c>
+      <c r="B177" t="s">
+        <v>32</v>
+      </c>
+      <c r="C177" t="s">
+        <v>33</v>
+      </c>
+      <c r="D177" t="s">
+        <v>264</v>
+      </c>
+      <c r="E177" t="s">
+        <v>35</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>265</v>
+      </c>
+      <c r="B178" t="s">
+        <v>32</v>
+      </c>
+      <c r="C178" t="s">
+        <v>33</v>
+      </c>
+      <c r="D178" t="s">
+        <v>266</v>
+      </c>
+      <c r="E178" t="s">
+        <v>35</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>267</v>
+      </c>
+      <c r="B179" t="s">
+        <v>32</v>
+      </c>
+      <c r="C179" t="s">
+        <v>33</v>
+      </c>
+      <c r="D179" t="s">
+        <v>268</v>
+      </c>
+      <c r="E179" t="s">
+        <v>35</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>269</v>
+      </c>
+      <c r="B180" t="s">
+        <v>32</v>
+      </c>
+      <c r="C180" t="s">
+        <v>33</v>
+      </c>
+      <c r="D180" t="s">
+        <v>270</v>
+      </c>
+      <c r="E180" t="s">
+        <v>35</v>
+      </c>
+      <c r="F180">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>271</v>
+      </c>
+      <c r="B181" t="s">
+        <v>32</v>
+      </c>
+      <c r="C181" t="s">
+        <v>33</v>
+      </c>
+      <c r="D181" t="s">
+        <v>145</v>
+      </c>
+      <c r="E181" t="s">
+        <v>35</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>258</v>
+      </c>
+      <c r="B182" t="s">
+        <v>32</v>
+      </c>
+      <c r="C182" t="s">
+        <v>33</v>
+      </c>
+      <c r="D182" t="s">
+        <v>272</v>
+      </c>
+      <c r="E182" t="s">
+        <v>35</v>
+      </c>
+      <c r="F182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>273</v>
+      </c>
+      <c r="B183" t="s">
+        <v>32</v>
+      </c>
+      <c r="C183" t="s">
+        <v>33</v>
+      </c>
+      <c r="D183" t="s">
+        <v>268</v>
+      </c>
+      <c r="E183" t="s">
+        <v>35</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>265</v>
+      </c>
+      <c r="B184" t="s">
+        <v>32</v>
+      </c>
+      <c r="C184" t="s">
+        <v>33</v>
+      </c>
+      <c r="D184" t="s">
+        <v>274</v>
+      </c>
+      <c r="E184" t="s">
+        <v>35</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>275</v>
+      </c>
+      <c r="B185" t="s">
+        <v>32</v>
+      </c>
+      <c r="C185" t="s">
+        <v>33</v>
+      </c>
+      <c r="D185" t="s">
+        <v>276</v>
+      </c>
+      <c r="E185" t="s">
+        <v>35</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>260</v>
+      </c>
+      <c r="B186" t="s">
+        <v>32</v>
+      </c>
+      <c r="C186" t="s">
+        <v>33</v>
+      </c>
+      <c r="D186" t="s">
+        <v>98</v>
+      </c>
+      <c r="E186" t="s">
+        <v>35</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>271</v>
+      </c>
+      <c r="B187" t="s">
+        <v>32</v>
+      </c>
+      <c r="C187" t="s">
+        <v>33</v>
+      </c>
+      <c r="D187" t="s">
+        <v>276</v>
+      </c>
+      <c r="E187" t="s">
+        <v>35</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>275</v>
+      </c>
+      <c r="B188" t="s">
+        <v>32</v>
+      </c>
+      <c r="C188" t="s">
+        <v>33</v>
+      </c>
+      <c r="D188" t="s">
+        <v>37</v>
+      </c>
+      <c r="E188" t="s">
+        <v>35</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>273</v>
+      </c>
+      <c r="B189" t="s">
+        <v>32</v>
+      </c>
+      <c r="C189" t="s">
+        <v>33</v>
+      </c>
+      <c r="D189" t="s">
+        <v>277</v>
+      </c>
+      <c r="E189" t="s">
+        <v>35</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>278</v>
+      </c>
+      <c r="B190" t="s">
+        <v>32</v>
+      </c>
+      <c r="C190" t="s">
+        <v>33</v>
+      </c>
+      <c r="D190" t="s">
+        <v>279</v>
+      </c>
+      <c r="E190" t="s">
+        <v>35</v>
+      </c>
+      <c r="F190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>275</v>
+      </c>
+      <c r="B191" t="s">
+        <v>32</v>
+      </c>
+      <c r="C191" t="s">
+        <v>33</v>
+      </c>
+      <c r="D191" t="s">
+        <v>88</v>
+      </c>
+      <c r="E191" t="s">
+        <v>35</v>
+      </c>
+      <c r="F191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>269</v>
+      </c>
+      <c r="B192" t="s">
+        <v>32</v>
+      </c>
+      <c r="C192" t="s">
+        <v>33</v>
+      </c>
+      <c r="D192" t="s">
+        <v>188</v>
+      </c>
+      <c r="E192" t="s">
+        <v>35</v>
+      </c>
+      <c r="F192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>280</v>
+      </c>
+      <c r="B193" t="s">
+        <v>32</v>
+      </c>
+      <c r="C193" t="s">
+        <v>33</v>
+      </c>
+      <c r="D193" t="s">
+        <v>281</v>
+      </c>
+      <c r="E193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>282</v>
+      </c>
+      <c r="B194" t="s">
+        <v>32</v>
+      </c>
+      <c r="C194" t="s">
+        <v>33</v>
+      </c>
+      <c r="D194" t="s">
+        <v>223</v>
+      </c>
+      <c r="E194" t="s">
+        <v>35</v>
+      </c>
+      <c r="F194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>283</v>
+      </c>
+      <c r="B195" t="s">
+        <v>32</v>
+      </c>
+      <c r="C195" t="s">
+        <v>33</v>
+      </c>
+      <c r="D195" t="s">
+        <v>284</v>
+      </c>
+      <c r="E195" t="s">
+        <v>35</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>280</v>
+      </c>
+      <c r="B196" t="s">
+        <v>32</v>
+      </c>
+      <c r="C196" t="s">
+        <v>33</v>
+      </c>
+      <c r="D196" t="s">
+        <v>126</v>
+      </c>
+      <c r="E196" t="s">
+        <v>35</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>267</v>
+      </c>
+      <c r="B197" t="s">
+        <v>32</v>
+      </c>
+      <c r="C197" t="s">
+        <v>33</v>
+      </c>
+      <c r="D197" t="s">
+        <v>285</v>
+      </c>
+      <c r="E197" t="s">
+        <v>35</v>
+      </c>
+      <c r="F197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>286</v>
+      </c>
+      <c r="B198" t="s">
+        <v>32</v>
+      </c>
+      <c r="C198" t="s">
+        <v>33</v>
+      </c>
+      <c r="D198" t="s">
+        <v>285</v>
+      </c>
+      <c r="E198" t="s">
+        <v>35</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>280</v>
+      </c>
+      <c r="B199" t="s">
+        <v>32</v>
+      </c>
+      <c r="C199" t="s">
+        <v>33</v>
+      </c>
+      <c r="D199" t="s">
+        <v>59</v>
+      </c>
+      <c r="E199" t="s">
+        <v>35</v>
+      </c>
+      <c r="F199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>275</v>
+      </c>
+      <c r="B200" t="s">
+        <v>32</v>
+      </c>
+      <c r="C200" t="s">
+        <v>33</v>
+      </c>
+      <c r="D200" t="s">
+        <v>287</v>
+      </c>
+      <c r="E200" t="s">
+        <v>35</v>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>273</v>
+      </c>
+      <c r="B201" t="s">
+        <v>32</v>
+      </c>
+      <c r="C201" t="s">
+        <v>33</v>
+      </c>
+      <c r="D201" t="s">
+        <v>288</v>
+      </c>
+      <c r="E201" t="s">
+        <v>35</v>
+      </c>
+      <c r="F201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>265</v>
+      </c>
+      <c r="B202" t="s">
+        <v>32</v>
+      </c>
+      <c r="C202" t="s">
+        <v>33</v>
+      </c>
+      <c r="D202" t="s">
+        <v>164</v>
+      </c>
+      <c r="E202" t="s">
+        <v>35</v>
+      </c>
+      <c r="F202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>289</v>
+      </c>
+      <c r="B203" t="s">
+        <v>32</v>
+      </c>
+      <c r="C203" t="s">
+        <v>33</v>
+      </c>
+      <c r="D203" t="s">
+        <v>290</v>
+      </c>
+      <c r="E203" t="s">
+        <v>35</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>291</v>
+      </c>
+      <c r="B204" t="s">
+        <v>32</v>
+      </c>
+      <c r="C204" t="s">
+        <v>33</v>
+      </c>
+      <c r="D204" t="s">
+        <v>126</v>
+      </c>
+      <c r="E204" t="s">
+        <v>35</v>
+      </c>
+      <c r="F204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>265</v>
+      </c>
+      <c r="B205" t="s">
+        <v>32</v>
+      </c>
+      <c r="C205" t="s">
+        <v>33</v>
+      </c>
+      <c r="D205" t="s">
+        <v>292</v>
+      </c>
+      <c r="E205" t="s">
+        <v>35</v>
+      </c>
+      <c r="F205">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>267</v>
+      </c>
+      <c r="B206" t="s">
+        <v>32</v>
+      </c>
+      <c r="C206" t="s">
+        <v>33</v>
+      </c>
+      <c r="D206" t="s">
+        <v>166</v>
+      </c>
+      <c r="E206" t="s">
+        <v>35</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>286</v>
+      </c>
+      <c r="B207" t="s">
+        <v>32</v>
+      </c>
+      <c r="C207" t="s">
+        <v>33</v>
+      </c>
+      <c r="D207" t="s">
+        <v>293</v>
+      </c>
+      <c r="E207" t="s">
+        <v>35</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>294</v>
+      </c>
+      <c r="B208" t="s">
+        <v>32</v>
+      </c>
+      <c r="C208" t="s">
+        <v>33</v>
+      </c>
+      <c r="D208" t="s">
+        <v>295</v>
+      </c>
+      <c r="E208" t="s">
+        <v>35</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>275</v>
+      </c>
+      <c r="B209" t="s">
+        <v>32</v>
+      </c>
+      <c r="C209" t="s">
+        <v>33</v>
+      </c>
+      <c r="D209" t="s">
+        <v>39</v>
+      </c>
+      <c r="E209" t="s">
+        <v>35</v>
+      </c>
+      <c r="F209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>273</v>
+      </c>
+      <c r="B210" t="s">
+        <v>32</v>
+      </c>
+      <c r="C210" t="s">
+        <v>33</v>
+      </c>
+      <c r="D210" t="s">
+        <v>296</v>
+      </c>
+      <c r="E210" t="s">
+        <v>35</v>
+      </c>
+      <c r="F210">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>294</v>
+      </c>
+      <c r="B211" t="s">
+        <v>32</v>
+      </c>
+      <c r="C211" t="s">
+        <v>33</v>
+      </c>
+      <c r="D211" t="s">
+        <v>297</v>
+      </c>
+      <c r="E211" t="s">
+        <v>35</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>258</v>
+      </c>
+      <c r="B212" t="s">
+        <v>32</v>
+      </c>
+      <c r="C212" t="s">
+        <v>33</v>
+      </c>
+      <c r="D212" t="s">
+        <v>189</v>
+      </c>
+      <c r="E212" t="s">
+        <v>35</v>
+      </c>
+      <c r="F212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>273</v>
+      </c>
+      <c r="B213" t="s">
+        <v>32</v>
+      </c>
+      <c r="C213" t="s">
+        <v>33</v>
+      </c>
+      <c r="D213" t="s">
+        <v>79</v>
+      </c>
+      <c r="E213" t="s">
+        <v>35</v>
+      </c>
+      <c r="F213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>280</v>
+      </c>
+      <c r="B214" t="s">
+        <v>32</v>
+      </c>
+      <c r="C214" t="s">
+        <v>33</v>
+      </c>
+      <c r="D214" t="s">
+        <v>298</v>
+      </c>
+      <c r="E214" t="s">
+        <v>35</v>
+      </c>
+      <c r="F214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>267</v>
+      </c>
+      <c r="B215" t="s">
+        <v>32</v>
+      </c>
+      <c r="C215" t="s">
+        <v>33</v>
+      </c>
+      <c r="D215" t="s">
+        <v>163</v>
+      </c>
+      <c r="E215" t="s">
+        <v>35</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>299</v>
+      </c>
+      <c r="B216" t="s">
+        <v>32</v>
+      </c>
+      <c r="C216" t="s">
+        <v>33</v>
+      </c>
+      <c r="D216" t="s">
+        <v>300</v>
+      </c>
+      <c r="E216" t="s">
+        <v>35</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>301</v>
+      </c>
+      <c r="B217" t="s">
+        <v>32</v>
+      </c>
+      <c r="C217" t="s">
+        <v>33</v>
+      </c>
+      <c r="D217" t="s">
+        <v>302</v>
+      </c>
+      <c r="E217" t="s">
+        <v>35</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>282</v>
+      </c>
+      <c r="B218" t="s">
+        <v>32</v>
+      </c>
+      <c r="C218" t="s">
+        <v>33</v>
+      </c>
+      <c r="D218" t="s">
+        <v>303</v>
+      </c>
+      <c r="E218" t="s">
+        <v>35</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>291</v>
+      </c>
+      <c r="B219" t="s">
+        <v>32</v>
+      </c>
+      <c r="C219" t="s">
+        <v>33</v>
+      </c>
+      <c r="D219" t="s">
+        <v>37</v>
+      </c>
+      <c r="E219" t="s">
+        <v>35</v>
+      </c>
+      <c r="F219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>271</v>
+      </c>
+      <c r="B220" t="s">
+        <v>32</v>
+      </c>
+      <c r="C220" t="s">
+        <v>33</v>
+      </c>
+      <c r="D220" t="s">
+        <v>304</v>
+      </c>
+      <c r="E220" t="s">
+        <v>35</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>275</v>
+      </c>
+      <c r="B221" t="s">
+        <v>32</v>
+      </c>
+      <c r="C221" t="s">
+        <v>33</v>
+      </c>
+      <c r="D221" t="s">
+        <v>305</v>
+      </c>
+      <c r="E221" t="s">
+        <v>35</v>
+      </c>
+      <c r="F221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>299</v>
+      </c>
+      <c r="B222" t="s">
+        <v>32</v>
+      </c>
+      <c r="C222" t="s">
+        <v>33</v>
+      </c>
+      <c r="D222" t="s">
+        <v>306</v>
+      </c>
+      <c r="E222" t="s">
+        <v>35</v>
+      </c>
+      <c r="F222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>280</v>
+      </c>
+      <c r="B223" t="s">
+        <v>32</v>
+      </c>
+      <c r="C223" t="s">
+        <v>33</v>
+      </c>
+      <c r="D223" t="s">
+        <v>285</v>
+      </c>
+      <c r="E223" t="s">
+        <v>35</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>267</v>
+      </c>
+      <c r="B224" t="s">
+        <v>32</v>
+      </c>
+      <c r="C224" t="s">
+        <v>33</v>
+      </c>
+      <c r="D224" t="s">
+        <v>307</v>
+      </c>
+      <c r="E224" t="s">
+        <v>35</v>
+      </c>
+      <c r="F224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>260</v>
+      </c>
+      <c r="B225" t="s">
+        <v>32</v>
+      </c>
+      <c r="C225" t="s">
+        <v>33</v>
+      </c>
+      <c r="D225" t="s">
+        <v>99</v>
+      </c>
+      <c r="E225" t="s">
+        <v>35</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>271</v>
+      </c>
+      <c r="B226" t="s">
+        <v>32</v>
+      </c>
+      <c r="C226" t="s">
+        <v>33</v>
+      </c>
+      <c r="D226" t="s">
+        <v>96</v>
+      </c>
+      <c r="E226" t="s">
+        <v>35</v>
+      </c>
+      <c r="F226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>282</v>
+      </c>
+      <c r="B227" t="s">
+        <v>32</v>
+      </c>
+      <c r="C227" t="s">
+        <v>33</v>
+      </c>
+      <c r="D227" t="s">
+        <v>308</v>
+      </c>
+      <c r="E227" t="s">
+        <v>35</v>
+      </c>
+      <c r="F227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>273</v>
+      </c>
+      <c r="B228" t="s">
+        <v>32</v>
+      </c>
+      <c r="C228" t="s">
+        <v>33</v>
+      </c>
+      <c r="D228" t="s">
+        <v>309</v>
+      </c>
+      <c r="E228" t="s">
+        <v>35</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>280</v>
+      </c>
+      <c r="B229" t="s">
+        <v>32</v>
+      </c>
+      <c r="C229" t="s">
+        <v>33</v>
+      </c>
+      <c r="D229" t="s">
+        <v>266</v>
+      </c>
+      <c r="E229" t="s">
+        <v>35</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>282</v>
+      </c>
+      <c r="B230" t="s">
+        <v>32</v>
+      </c>
+      <c r="C230" t="s">
+        <v>33</v>
+      </c>
+      <c r="D230" t="s">
+        <v>310</v>
+      </c>
+      <c r="E230" t="s">
+        <v>35</v>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>299</v>
+      </c>
+      <c r="B231" t="s">
+        <v>32</v>
+      </c>
+      <c r="C231" t="s">
+        <v>33</v>
+      </c>
+      <c r="D231" t="s">
+        <v>311</v>
+      </c>
+      <c r="E231" t="s">
+        <v>35</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>265</v>
+      </c>
+      <c r="B232" t="s">
+        <v>32</v>
+      </c>
+      <c r="C232" t="s">
+        <v>33</v>
+      </c>
+      <c r="D232" t="s">
         <v>84</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E232" t="s">
+        <v>35</v>
+      </c>
+      <c r="F232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>312</v>
+      </c>
+      <c r="B233" t="s">
+        <v>32</v>
+      </c>
+      <c r="C233" t="s">
+        <v>33</v>
+      </c>
+      <c r="D233" t="s">
+        <v>313</v>
+      </c>
+      <c r="E233" t="s">
+        <v>35</v>
+      </c>
+      <c r="F233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>286</v>
+      </c>
+      <c r="B234" t="s">
+        <v>32</v>
+      </c>
+      <c r="C234" t="s">
+        <v>33</v>
+      </c>
+      <c r="D234" t="s">
+        <v>314</v>
+      </c>
+      <c r="E234" t="s">
+        <v>35</v>
+      </c>
+      <c r="F234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>315</v>
+      </c>
+      <c r="B235" t="s">
+        <v>104</v>
+      </c>
+      <c r="C235" t="s">
+        <v>105</v>
+      </c>
+      <c r="D235" t="s">
+        <v>77</v>
+      </c>
+      <c r="E235" t="s">
+        <v>316</v>
+      </c>
+      <c r="F235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>317</v>
+      </c>
+      <c r="B236" t="s">
+        <v>104</v>
+      </c>
+      <c r="C236" t="s">
+        <v>105</v>
+      </c>
+      <c r="D236" t="s">
+        <v>86</v>
+      </c>
+      <c r="E236" t="s">
+        <v>316</v>
+      </c>
+      <c r="F236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>318</v>
+      </c>
+      <c r="B237" t="s">
+        <v>104</v>
+      </c>
+      <c r="C237" t="s">
+        <v>105</v>
+      </c>
+      <c r="D237" t="s">
+        <v>319</v>
+      </c>
+      <c r="E237" t="s">
+        <v>316</v>
+      </c>
+      <c r="F237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>320</v>
+      </c>
+      <c r="B238" t="s">
+        <v>104</v>
+      </c>
+      <c r="C238" t="s">
+        <v>105</v>
+      </c>
+      <c r="D238" t="s">
+        <v>53</v>
+      </c>
+      <c r="E238" t="s">
+        <v>316</v>
+      </c>
+      <c r="F238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>321</v>
+      </c>
+      <c r="B239" t="s">
+        <v>104</v>
+      </c>
+      <c r="C239" t="s">
+        <v>105</v>
+      </c>
+      <c r="D239" t="s">
+        <v>322</v>
+      </c>
+      <c r="E239" t="s">
+        <v>316</v>
+      </c>
+      <c r="F239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>247</v>
+      </c>
+      <c r="B240" t="s">
+        <v>104</v>
+      </c>
+      <c r="C240" t="s">
+        <v>105</v>
+      </c>
+      <c r="D240" t="s">
+        <v>75</v>
+      </c>
+      <c r="E240" t="s">
+        <v>316</v>
+      </c>
+      <c r="F240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>323</v>
+      </c>
+      <c r="B241" t="s">
+        <v>104</v>
+      </c>
+      <c r="C241" t="s">
+        <v>105</v>
+      </c>
+      <c r="D241" t="s">
         <v>74</v>
       </c>
-      <c r="E98" t="s">
-        <v>86</v>
-      </c>
-      <c r="F98">
-        <v>2</v>
+      <c r="E241" t="s">
+        <v>316</v>
+      </c>
+      <c r="F241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>321</v>
+      </c>
+      <c r="B242" t="s">
+        <v>104</v>
+      </c>
+      <c r="C242" t="s">
+        <v>105</v>
+      </c>
+      <c r="D242" t="s">
+        <v>324</v>
+      </c>
+      <c r="E242" t="s">
+        <v>316</v>
+      </c>
+      <c r="F242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>325</v>
+      </c>
+      <c r="B243" t="s">
+        <v>104</v>
+      </c>
+      <c r="C243" t="s">
+        <v>105</v>
+      </c>
+      <c r="D243" t="s">
+        <v>326</v>
+      </c>
+      <c r="E243" t="s">
+        <v>316</v>
+      </c>
+      <c r="F243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>327</v>
+      </c>
+      <c r="B244" t="s">
+        <v>104</v>
+      </c>
+      <c r="C244" t="s">
+        <v>105</v>
+      </c>
+      <c r="D244" t="s">
+        <v>122</v>
+      </c>
+      <c r="E244" t="s">
+        <v>316</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>328</v>
+      </c>
+      <c r="B245" t="s">
+        <v>104</v>
+      </c>
+      <c r="C245" t="s">
+        <v>105</v>
+      </c>
+      <c r="D245" t="s">
+        <v>329</v>
+      </c>
+      <c r="E245" t="s">
+        <v>316</v>
+      </c>
+      <c r="F245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>330</v>
+      </c>
+      <c r="B246" t="s">
+        <v>104</v>
+      </c>
+      <c r="C246" t="s">
+        <v>105</v>
+      </c>
+      <c r="D246" t="s">
+        <v>331</v>
+      </c>
+      <c r="E246" t="s">
+        <v>316</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>332</v>
+      </c>
+      <c r="B247" t="s">
+        <v>104</v>
+      </c>
+      <c r="C247" t="s">
+        <v>105</v>
+      </c>
+      <c r="D247" t="s">
+        <v>333</v>
+      </c>
+      <c r="E247" t="s">
+        <v>316</v>
+      </c>
+      <c r="F247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>334</v>
+      </c>
+      <c r="B248" t="s">
+        <v>104</v>
+      </c>
+      <c r="C248" t="s">
+        <v>105</v>
+      </c>
+      <c r="D248" t="s">
+        <v>335</v>
+      </c>
+      <c r="E248" t="s">
+        <v>316</v>
+      </c>
+      <c r="F248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>336</v>
+      </c>
+      <c r="B249" t="s">
+        <v>104</v>
+      </c>
+      <c r="C249" t="s">
+        <v>105</v>
+      </c>
+      <c r="D249" t="s">
+        <v>337</v>
+      </c>
+      <c r="E249" t="s">
+        <v>316</v>
+      </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>315</v>
+      </c>
+      <c r="B250" t="s">
+        <v>104</v>
+      </c>
+      <c r="C250" t="s">
+        <v>105</v>
+      </c>
+      <c r="D250" t="s">
+        <v>148</v>
+      </c>
+      <c r="E250" t="s">
+        <v>316</v>
+      </c>
+      <c r="F250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>338</v>
+      </c>
+      <c r="B251" t="s">
+        <v>104</v>
+      </c>
+      <c r="C251" t="s">
+        <v>105</v>
+      </c>
+      <c r="D251" t="s">
+        <v>339</v>
+      </c>
+      <c r="E251" t="s">
+        <v>316</v>
+      </c>
+      <c r="F251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>340</v>
+      </c>
+      <c r="B252" t="s">
+        <v>104</v>
+      </c>
+      <c r="C252" t="s">
+        <v>105</v>
+      </c>
+      <c r="D252" t="s">
+        <v>341</v>
+      </c>
+      <c r="E252" t="s">
+        <v>316</v>
+      </c>
+      <c r="F252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>342</v>
+      </c>
+      <c r="B253" t="s">
+        <v>104</v>
+      </c>
+      <c r="C253" t="s">
+        <v>105</v>
+      </c>
+      <c r="D253" t="s">
+        <v>343</v>
+      </c>
+      <c r="E253" t="s">
+        <v>316</v>
+      </c>
+      <c r="F253">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>317</v>
+      </c>
+      <c r="B254" t="s">
+        <v>104</v>
+      </c>
+      <c r="C254" t="s">
+        <v>105</v>
+      </c>
+      <c r="D254" t="s">
+        <v>344</v>
+      </c>
+      <c r="E254" t="s">
+        <v>316</v>
+      </c>
+      <c r="F254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>345</v>
+      </c>
+      <c r="B255" t="s">
+        <v>104</v>
+      </c>
+      <c r="C255" t="s">
+        <v>105</v>
+      </c>
+      <c r="D255" t="s">
+        <v>346</v>
+      </c>
+      <c r="E255" t="s">
+        <v>316</v>
+      </c>
+      <c r="F255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>347</v>
+      </c>
+      <c r="B256" t="s">
+        <v>104</v>
+      </c>
+      <c r="C256" t="s">
+        <v>105</v>
+      </c>
+      <c r="D256" t="s">
+        <v>348</v>
+      </c>
+      <c r="E256" t="s">
+        <v>316</v>
+      </c>
+      <c r="F256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>334</v>
+      </c>
+      <c r="B257" t="s">
+        <v>104</v>
+      </c>
+      <c r="C257" t="s">
+        <v>105</v>
+      </c>
+      <c r="D257" t="s">
+        <v>349</v>
+      </c>
+      <c r="E257" t="s">
+        <v>316</v>
+      </c>
+      <c r="F257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>350</v>
+      </c>
+      <c r="B258" t="s">
+        <v>104</v>
+      </c>
+      <c r="C258" t="s">
+        <v>105</v>
+      </c>
+      <c r="D258" t="s">
+        <v>351</v>
+      </c>
+      <c r="E258" t="s">
+        <v>316</v>
+      </c>
+      <c r="F258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>352</v>
+      </c>
+      <c r="B259" t="s">
+        <v>104</v>
+      </c>
+      <c r="C259" t="s">
+        <v>105</v>
+      </c>
+      <c r="D259" t="s">
+        <v>353</v>
+      </c>
+      <c r="E259" t="s">
+        <v>316</v>
+      </c>
+      <c r="F259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>354</v>
+      </c>
+      <c r="B260" t="s">
+        <v>104</v>
+      </c>
+      <c r="C260" t="s">
+        <v>105</v>
+      </c>
+      <c r="D260" t="s">
+        <v>293</v>
+      </c>
+      <c r="E260" t="s">
+        <v>316</v>
+      </c>
+      <c r="F260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>355</v>
+      </c>
+      <c r="B261" t="s">
+        <v>104</v>
+      </c>
+      <c r="C261" t="s">
+        <v>105</v>
+      </c>
+      <c r="D261" t="s">
+        <v>313</v>
+      </c>
+      <c r="E261" t="s">
+        <v>316</v>
+      </c>
+      <c r="F261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>356</v>
+      </c>
+      <c r="B262" t="s">
+        <v>104</v>
+      </c>
+      <c r="C262" t="s">
+        <v>105</v>
+      </c>
+      <c r="D262" t="s">
+        <v>357</v>
+      </c>
+      <c r="E262" t="s">
+        <v>316</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>358</v>
+      </c>
+      <c r="B263" t="s">
+        <v>104</v>
+      </c>
+      <c r="C263" t="s">
+        <v>105</v>
+      </c>
+      <c r="D263" t="s">
+        <v>359</v>
+      </c>
+      <c r="E263" t="s">
+        <v>316</v>
+      </c>
+      <c r="F263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>360</v>
+      </c>
+      <c r="B264" t="s">
+        <v>104</v>
+      </c>
+      <c r="C264" t="s">
+        <v>105</v>
+      </c>
+      <c r="D264" t="s">
+        <v>361</v>
+      </c>
+      <c r="E264" t="s">
+        <v>316</v>
+      </c>
+      <c r="F264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>362</v>
+      </c>
+      <c r="B265" t="s">
+        <v>104</v>
+      </c>
+      <c r="C265" t="s">
+        <v>105</v>
+      </c>
+      <c r="D265" t="s">
+        <v>363</v>
+      </c>
+      <c r="E265" t="s">
+        <v>316</v>
+      </c>
+      <c r="F265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>364</v>
+      </c>
+      <c r="B266" t="s">
+        <v>104</v>
+      </c>
+      <c r="C266" t="s">
+        <v>105</v>
+      </c>
+      <c r="D266" t="s">
+        <v>365</v>
+      </c>
+      <c r="E266" t="s">
+        <v>316</v>
+      </c>
+      <c r="F266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>366</v>
+      </c>
+      <c r="B267" t="s">
+        <v>104</v>
+      </c>
+      <c r="C267" t="s">
+        <v>105</v>
+      </c>
+      <c r="D267" t="s">
+        <v>367</v>
+      </c>
+      <c r="E267" t="s">
+        <v>316</v>
+      </c>
+      <c r="F267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>320</v>
+      </c>
+      <c r="B268" t="s">
+        <v>104</v>
+      </c>
+      <c r="C268" t="s">
+        <v>105</v>
+      </c>
+      <c r="D268" t="s">
+        <v>368</v>
+      </c>
+      <c r="E268" t="s">
+        <v>316</v>
+      </c>
+      <c r="F268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>369</v>
+      </c>
+      <c r="B269" t="s">
+        <v>104</v>
+      </c>
+      <c r="C269" t="s">
+        <v>105</v>
+      </c>
+      <c r="D269" t="s">
+        <v>370</v>
+      </c>
+      <c r="E269" t="s">
+        <v>316</v>
+      </c>
+      <c r="F269">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>371</v>
+      </c>
+      <c r="B270" t="s">
+        <v>104</v>
+      </c>
+      <c r="C270" t="s">
+        <v>105</v>
+      </c>
+      <c r="D270" t="s">
+        <v>372</v>
+      </c>
+      <c r="E270" t="s">
+        <v>316</v>
+      </c>
+      <c r="F270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>373</v>
+      </c>
+      <c r="B271" t="s">
+        <v>104</v>
+      </c>
+      <c r="C271" t="s">
+        <v>105</v>
+      </c>
+      <c r="D271" t="s">
+        <v>95</v>
+      </c>
+      <c r="E271" t="s">
+        <v>316</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>328</v>
+      </c>
+      <c r="B272" t="s">
+        <v>104</v>
+      </c>
+      <c r="C272" t="s">
+        <v>105</v>
+      </c>
+      <c r="D272" t="s">
+        <v>374</v>
+      </c>
+      <c r="E272" t="s">
+        <v>316</v>
+      </c>
+      <c r="F272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>318</v>
+      </c>
+      <c r="B273" t="s">
+        <v>104</v>
+      </c>
+      <c r="C273" t="s">
+        <v>105</v>
+      </c>
+      <c r="D273" t="s">
+        <v>375</v>
+      </c>
+      <c r="E273" t="s">
+        <v>316</v>
+      </c>
+      <c r="F273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>376</v>
+      </c>
+      <c r="B274" t="s">
+        <v>104</v>
+      </c>
+      <c r="C274" t="s">
+        <v>105</v>
+      </c>
+      <c r="D274" t="s">
+        <v>377</v>
+      </c>
+      <c r="E274" t="s">
+        <v>316</v>
+      </c>
+      <c r="F274">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>378</v>
+      </c>
+      <c r="B275" t="s">
+        <v>104</v>
+      </c>
+      <c r="C275" t="s">
+        <v>105</v>
+      </c>
+      <c r="D275" t="s">
+        <v>367</v>
+      </c>
+      <c r="E275" t="s">
+        <v>316</v>
+      </c>
+      <c r="F275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>247</v>
+      </c>
+      <c r="B276" t="s">
+        <v>104</v>
+      </c>
+      <c r="C276" t="s">
+        <v>105</v>
+      </c>
+      <c r="D276" t="s">
+        <v>379</v>
+      </c>
+      <c r="E276" t="s">
+        <v>316</v>
+      </c>
+      <c r="F276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>380</v>
+      </c>
+      <c r="B277" t="s">
+        <v>104</v>
+      </c>
+      <c r="C277" t="s">
+        <v>105</v>
+      </c>
+      <c r="D277" t="s">
+        <v>381</v>
+      </c>
+      <c r="E277" t="s">
+        <v>316</v>
+      </c>
+      <c r="F277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>382</v>
+      </c>
+      <c r="B278" t="s">
+        <v>104</v>
+      </c>
+      <c r="C278" t="s">
+        <v>105</v>
+      </c>
+      <c r="D278" t="s">
+        <v>383</v>
+      </c>
+      <c r="E278" t="s">
+        <v>316</v>
+      </c>
+      <c r="F278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>243</v>
+      </c>
+      <c r="B279" t="s">
+        <v>104</v>
+      </c>
+      <c r="C279" t="s">
+        <v>105</v>
+      </c>
+      <c r="D279" t="s">
+        <v>225</v>
+      </c>
+      <c r="E279" t="s">
+        <v>316</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>384</v>
+      </c>
+      <c r="B280" t="s">
+        <v>104</v>
+      </c>
+      <c r="C280" t="s">
+        <v>105</v>
+      </c>
+      <c r="D280" t="s">
+        <v>385</v>
+      </c>
+      <c r="E280" t="s">
+        <v>316</v>
+      </c>
+      <c r="F280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>386</v>
+      </c>
+      <c r="B281" t="s">
+        <v>104</v>
+      </c>
+      <c r="C281" t="s">
+        <v>105</v>
+      </c>
+      <c r="D281" t="s">
+        <v>387</v>
+      </c>
+      <c r="E281" t="s">
+        <v>316</v>
+      </c>
+      <c r="F281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>388</v>
+      </c>
+      <c r="B282" t="s">
+        <v>104</v>
+      </c>
+      <c r="C282" t="s">
+        <v>105</v>
+      </c>
+      <c r="D282" t="s">
+        <v>389</v>
+      </c>
+      <c r="E282" t="s">
+        <v>316</v>
+      </c>
+      <c r="F282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>323</v>
+      </c>
+      <c r="B283" t="s">
+        <v>104</v>
+      </c>
+      <c r="C283" t="s">
+        <v>105</v>
+      </c>
+      <c r="D283" t="s">
+        <v>390</v>
+      </c>
+      <c r="E283" t="s">
+        <v>316</v>
+      </c>
+      <c r="F283">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>382</v>
+      </c>
+      <c r="B284" t="s">
+        <v>104</v>
+      </c>
+      <c r="C284" t="s">
+        <v>105</v>
+      </c>
+      <c r="D284" t="s">
+        <v>391</v>
+      </c>
+      <c r="E284" t="s">
+        <v>316</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>355</v>
+      </c>
+      <c r="B285" t="s">
+        <v>104</v>
+      </c>
+      <c r="C285" t="s">
+        <v>105</v>
+      </c>
+      <c r="D285" t="s">
+        <v>392</v>
+      </c>
+      <c r="E285" t="s">
+        <v>316</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>393</v>
+      </c>
+      <c r="B286" t="s">
+        <v>104</v>
+      </c>
+      <c r="C286" t="s">
+        <v>105</v>
+      </c>
+      <c r="D286" t="s">
+        <v>394</v>
+      </c>
+      <c r="E286" t="s">
+        <v>316</v>
+      </c>
+      <c r="F286">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>395</v>
+      </c>
+      <c r="B287" t="s">
+        <v>104</v>
+      </c>
+      <c r="C287" t="s">
+        <v>105</v>
+      </c>
+      <c r="D287" t="s">
+        <v>396</v>
+      </c>
+      <c r="E287" t="s">
+        <v>316</v>
+      </c>
+      <c r="F287">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>397</v>
+      </c>
+      <c r="B288" t="s">
+        <v>104</v>
+      </c>
+      <c r="C288" t="s">
+        <v>105</v>
+      </c>
+      <c r="D288" t="s">
+        <v>164</v>
+      </c>
+      <c r="E288" t="s">
+        <v>316</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>398</v>
+      </c>
+      <c r="B289" t="s">
+        <v>104</v>
+      </c>
+      <c r="C289" t="s">
+        <v>105</v>
+      </c>
+      <c r="D289" t="s">
+        <v>399</v>
+      </c>
+      <c r="E289" t="s">
+        <v>316</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>328</v>
+      </c>
+      <c r="B290" t="s">
+        <v>104</v>
+      </c>
+      <c r="C290" t="s">
+        <v>105</v>
+      </c>
+      <c r="D290" t="s">
+        <v>400</v>
+      </c>
+      <c r="E290" t="s">
+        <v>316</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>401</v>
+      </c>
+      <c r="B291" t="s">
+        <v>104</v>
+      </c>
+      <c r="C291" t="s">
+        <v>180</v>
+      </c>
+      <c r="D291" t="s">
+        <v>402</v>
+      </c>
+      <c r="E291" t="s">
+        <v>403</v>
+      </c>
+      <c r="F291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>384</v>
+      </c>
+      <c r="B292" t="s">
+        <v>104</v>
+      </c>
+      <c r="C292" t="s">
+        <v>180</v>
+      </c>
+      <c r="D292" t="s">
+        <v>404</v>
+      </c>
+      <c r="E292" t="s">
+        <v>403</v>
+      </c>
+      <c r="F292">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>358</v>
+      </c>
+      <c r="B293" t="s">
+        <v>104</v>
+      </c>
+      <c r="C293" t="s">
+        <v>180</v>
+      </c>
+      <c r="D293" t="s">
+        <v>405</v>
+      </c>
+      <c r="E293" t="s">
+        <v>403</v>
+      </c>
+      <c r="F293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>406</v>
+      </c>
+      <c r="B294" t="s">
+        <v>104</v>
+      </c>
+      <c r="C294" t="s">
+        <v>180</v>
+      </c>
+      <c r="D294" t="s">
+        <v>407</v>
+      </c>
+      <c r="E294" t="s">
+        <v>403</v>
+      </c>
+      <c r="F294">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>320</v>
+      </c>
+      <c r="B295" t="s">
+        <v>104</v>
+      </c>
+      <c r="C295" t="s">
+        <v>180</v>
+      </c>
+      <c r="D295" t="s">
+        <v>408</v>
+      </c>
+      <c r="E295" t="s">
+        <v>403</v>
+      </c>
+      <c r="F295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>409</v>
+      </c>
+      <c r="B296" t="s">
+        <v>104</v>
+      </c>
+      <c r="C296" t="s">
+        <v>180</v>
+      </c>
+      <c r="D296" t="s">
+        <v>92</v>
+      </c>
+      <c r="E296" t="s">
+        <v>403</v>
+      </c>
+      <c r="F296">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>401</v>
+      </c>
+      <c r="B297" t="s">
+        <v>104</v>
+      </c>
+      <c r="C297" t="s">
+        <v>180</v>
+      </c>
+      <c r="D297" t="s">
+        <v>410</v>
+      </c>
+      <c r="E297" t="s">
+        <v>403</v>
+      </c>
+      <c r="F297">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>411</v>
+      </c>
+      <c r="B298" t="s">
+        <v>104</v>
+      </c>
+      <c r="C298" t="s">
+        <v>180</v>
+      </c>
+      <c r="D298" t="s">
+        <v>174</v>
+      </c>
+      <c r="E298" t="s">
+        <v>403</v>
+      </c>
+      <c r="F298">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>412</v>
+      </c>
+      <c r="B299" t="s">
+        <v>104</v>
+      </c>
+      <c r="C299" t="s">
+        <v>180</v>
+      </c>
+      <c r="D299" t="s">
+        <v>161</v>
+      </c>
+      <c r="E299" t="s">
+        <v>403</v>
+      </c>
+      <c r="F299">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>244</v>
+      </c>
+      <c r="B300" t="s">
+        <v>104</v>
+      </c>
+      <c r="C300" t="s">
+        <v>180</v>
+      </c>
+      <c r="D300" t="s">
+        <v>413</v>
+      </c>
+      <c r="E300" t="s">
+        <v>403</v>
+      </c>
+      <c r="F300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>376</v>
+      </c>
+      <c r="B301" t="s">
+        <v>104</v>
+      </c>
+      <c r="C301" t="s">
+        <v>180</v>
+      </c>
+      <c r="D301" t="s">
+        <v>414</v>
+      </c>
+      <c r="E301" t="s">
+        <v>403</v>
+      </c>
+      <c r="F301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>328</v>
+      </c>
+      <c r="B302" t="s">
+        <v>104</v>
+      </c>
+      <c r="C302" t="s">
+        <v>180</v>
+      </c>
+      <c r="D302" t="s">
+        <v>171</v>
+      </c>
+      <c r="E302" t="s">
+        <v>403</v>
+      </c>
+      <c r="F302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>415</v>
+      </c>
+      <c r="B303" t="s">
+        <v>104</v>
+      </c>
+      <c r="C303" t="s">
+        <v>180</v>
+      </c>
+      <c r="D303" t="s">
+        <v>120</v>
+      </c>
+      <c r="E303" t="s">
+        <v>403</v>
+      </c>
+      <c r="F303">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>416</v>
+      </c>
+      <c r="B304" t="s">
+        <v>104</v>
+      </c>
+      <c r="C304" t="s">
+        <v>180</v>
+      </c>
+      <c r="D304" t="s">
+        <v>87</v>
+      </c>
+      <c r="E304" t="s">
+        <v>403</v>
+      </c>
+      <c r="F304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>417</v>
+      </c>
+      <c r="B305" t="s">
+        <v>104</v>
+      </c>
+      <c r="C305" t="s">
+        <v>180</v>
+      </c>
+      <c r="D305" t="s">
+        <v>367</v>
+      </c>
+      <c r="E305" t="s">
+        <v>403</v>
+      </c>
+      <c r="F305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>418</v>
+      </c>
+      <c r="B306" t="s">
+        <v>104</v>
+      </c>
+      <c r="C306" t="s">
+        <v>180</v>
+      </c>
+      <c r="D306" t="s">
+        <v>419</v>
+      </c>
+      <c r="E306" t="s">
+        <v>403</v>
+      </c>
+      <c r="F306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>362</v>
+      </c>
+      <c r="B307" t="s">
+        <v>104</v>
+      </c>
+      <c r="C307" t="s">
+        <v>180</v>
+      </c>
+      <c r="D307" t="s">
+        <v>281</v>
+      </c>
+      <c r="E307" t="s">
+        <v>403</v>
+      </c>
+      <c r="F307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>420</v>
+      </c>
+      <c r="B308" t="s">
+        <v>104</v>
+      </c>
+      <c r="C308" t="s">
+        <v>180</v>
+      </c>
+      <c r="D308" t="s">
+        <v>133</v>
+      </c>
+      <c r="E308" t="s">
+        <v>403</v>
+      </c>
+      <c r="F308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>421</v>
+      </c>
+      <c r="B309" t="s">
+        <v>104</v>
+      </c>
+      <c r="C309" t="s">
+        <v>180</v>
+      </c>
+      <c r="D309" t="s">
+        <v>422</v>
+      </c>
+      <c r="E309" t="s">
+        <v>403</v>
+      </c>
+      <c r="F309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>320</v>
+      </c>
+      <c r="B310" t="s">
+        <v>104</v>
+      </c>
+      <c r="C310" t="s">
+        <v>180</v>
+      </c>
+      <c r="D310" t="s">
+        <v>423</v>
+      </c>
+      <c r="E310" t="s">
+        <v>403</v>
+      </c>
+      <c r="F310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>364</v>
+      </c>
+      <c r="B311" t="s">
+        <v>104</v>
+      </c>
+      <c r="C311" t="s">
+        <v>180</v>
+      </c>
+      <c r="D311" t="s">
+        <v>424</v>
+      </c>
+      <c r="E311" t="s">
+        <v>403</v>
+      </c>
+      <c r="F311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>251</v>
+      </c>
+      <c r="B312" t="s">
+        <v>209</v>
+      </c>
+      <c r="C312" t="s">
+        <v>105</v>
+      </c>
+      <c r="D312" t="s">
+        <v>361</v>
+      </c>
+      <c r="E312" t="s">
+        <v>211</v>
+      </c>
+      <c r="F312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>425</v>
+      </c>
+      <c r="B313" t="s">
+        <v>209</v>
+      </c>
+      <c r="C313" t="s">
+        <v>105</v>
+      </c>
+      <c r="D313" t="s">
+        <v>426</v>
+      </c>
+      <c r="E313" t="s">
+        <v>211</v>
+      </c>
+      <c r="F313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>427</v>
+      </c>
+      <c r="B314" t="s">
+        <v>209</v>
+      </c>
+      <c r="C314" t="s">
+        <v>105</v>
+      </c>
+      <c r="D314" t="s">
+        <v>428</v>
+      </c>
+      <c r="E314" t="s">
+        <v>211</v>
+      </c>
+      <c r="F314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>250</v>
+      </c>
+      <c r="B315" t="s">
+        <v>209</v>
+      </c>
+      <c r="C315" t="s">
+        <v>105</v>
+      </c>
+      <c r="D315" t="s">
+        <v>370</v>
+      </c>
+      <c r="E315" t="s">
+        <v>211</v>
+      </c>
+      <c r="F315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>429</v>
+      </c>
+      <c r="B316" t="s">
+        <v>209</v>
+      </c>
+      <c r="C316" t="s">
+        <v>105</v>
+      </c>
+      <c r="D316" t="s">
+        <v>233</v>
+      </c>
+      <c r="E316" t="s">
+        <v>211</v>
+      </c>
+      <c r="F316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>430</v>
+      </c>
+      <c r="B317" t="s">
+        <v>209</v>
+      </c>
+      <c r="C317" t="s">
+        <v>105</v>
+      </c>
+      <c r="D317" t="s">
+        <v>431</v>
+      </c>
+      <c r="E317" t="s">
+        <v>211</v>
+      </c>
+      <c r="F317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>432</v>
+      </c>
+      <c r="B318" t="s">
+        <v>209</v>
+      </c>
+      <c r="C318" t="s">
+        <v>105</v>
+      </c>
+      <c r="D318" t="s">
+        <v>433</v>
+      </c>
+      <c r="E318" t="s">
+        <v>211</v>
+      </c>
+      <c r="F318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>429</v>
+      </c>
+      <c r="B319" t="s">
+        <v>209</v>
+      </c>
+      <c r="C319" t="s">
+        <v>105</v>
+      </c>
+      <c r="D319" t="s">
+        <v>434</v>
+      </c>
+      <c r="E319" t="s">
+        <v>211</v>
+      </c>
+      <c r="F319">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>435</v>
+      </c>
+      <c r="B320" t="s">
+        <v>209</v>
+      </c>
+      <c r="C320" t="s">
+        <v>105</v>
+      </c>
+      <c r="D320" t="s">
+        <v>400</v>
+      </c>
+      <c r="E320" t="s">
+        <v>211</v>
+      </c>
+      <c r="F320">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>436</v>
+      </c>
+      <c r="B321" t="s">
+        <v>209</v>
+      </c>
+      <c r="C321" t="s">
+        <v>105</v>
+      </c>
+      <c r="D321" t="s">
+        <v>344</v>
+      </c>
+      <c r="E321" t="s">
+        <v>211</v>
+      </c>
+      <c r="F321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>437</v>
+      </c>
+      <c r="B322" t="s">
+        <v>209</v>
+      </c>
+      <c r="C322" t="s">
+        <v>105</v>
+      </c>
+      <c r="D322" t="s">
+        <v>298</v>
+      </c>
+      <c r="E322" t="s">
+        <v>211</v>
+      </c>
+      <c r="F322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>438</v>
+      </c>
+      <c r="B323" t="s">
+        <v>209</v>
+      </c>
+      <c r="C323" t="s">
+        <v>105</v>
+      </c>
+      <c r="D323" t="s">
+        <v>372</v>
+      </c>
+      <c r="E323" t="s">
+        <v>211</v>
+      </c>
+      <c r="F323">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>439</v>
+      </c>
+      <c r="B324" t="s">
+        <v>209</v>
+      </c>
+      <c r="C324" t="s">
+        <v>105</v>
+      </c>
+      <c r="D324" t="s">
+        <v>68</v>
+      </c>
+      <c r="E324" t="s">
+        <v>211</v>
+      </c>
+      <c r="F324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>440</v>
+      </c>
+      <c r="B325" t="s">
+        <v>209</v>
+      </c>
+      <c r="C325" t="s">
+        <v>105</v>
+      </c>
+      <c r="D325" t="s">
+        <v>441</v>
+      </c>
+      <c r="E325" t="s">
+        <v>211</v>
+      </c>
+      <c r="F325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>442</v>
+      </c>
+      <c r="B326" t="s">
+        <v>209</v>
+      </c>
+      <c r="C326" t="s">
+        <v>105</v>
+      </c>
+      <c r="D326" t="s">
+        <v>287</v>
+      </c>
+      <c r="E326" t="s">
+        <v>211</v>
+      </c>
+      <c r="F326">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>443</v>
+      </c>
+      <c r="B327" t="s">
+        <v>444</v>
+      </c>
+      <c r="C327" t="s">
+        <v>445</v>
+      </c>
+      <c r="D327" t="s">
+        <v>122</v>
+      </c>
+      <c r="E327" t="s">
+        <v>446</v>
+      </c>
+      <c r="F327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>447</v>
+      </c>
+      <c r="B328" t="s">
+        <v>444</v>
+      </c>
+      <c r="C328" t="s">
+        <v>445</v>
+      </c>
+      <c r="D328" t="s">
+        <v>448</v>
+      </c>
+      <c r="E328" t="s">
+        <v>446</v>
+      </c>
+      <c r="F328">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>449</v>
+      </c>
+      <c r="B329" t="s">
+        <v>444</v>
+      </c>
+      <c r="C329" t="s">
+        <v>445</v>
+      </c>
+      <c r="D329" t="s">
+        <v>450</v>
+      </c>
+      <c r="E329" t="s">
+        <v>446</v>
+      </c>
+      <c r="F329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>252</v>
+      </c>
+      <c r="B330" t="s">
+        <v>444</v>
+      </c>
+      <c r="C330" t="s">
+        <v>445</v>
+      </c>
+      <c r="D330" t="s">
+        <v>451</v>
+      </c>
+      <c r="E330" t="s">
+        <v>446</v>
+      </c>
+      <c r="F330">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>452</v>
+      </c>
+      <c r="B331" t="s">
+        <v>444</v>
+      </c>
+      <c r="C331" t="s">
+        <v>445</v>
+      </c>
+      <c r="D331" t="s">
+        <v>365</v>
+      </c>
+      <c r="E331" t="s">
+        <v>446</v>
+      </c>
+      <c r="F331">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>449</v>
+      </c>
+      <c r="B332" t="s">
+        <v>444</v>
+      </c>
+      <c r="C332" t="s">
+        <v>445</v>
+      </c>
+      <c r="D332" t="s">
+        <v>453</v>
+      </c>
+      <c r="E332" t="s">
+        <v>446</v>
+      </c>
+      <c r="F332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>454</v>
+      </c>
+      <c r="B333" t="s">
+        <v>444</v>
+      </c>
+      <c r="C333" t="s">
+        <v>445</v>
+      </c>
+      <c r="D333" t="s">
+        <v>455</v>
+      </c>
+      <c r="E333" t="s">
+        <v>446</v>
+      </c>
+      <c r="F333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>456</v>
+      </c>
+      <c r="B334" t="s">
+        <v>444</v>
+      </c>
+      <c r="C334" t="s">
+        <v>445</v>
+      </c>
+      <c r="D334" t="s">
+        <v>99</v>
+      </c>
+      <c r="E334" t="s">
+        <v>446</v>
+      </c>
+      <c r="F334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>457</v>
+      </c>
+      <c r="B335" t="s">
+        <v>444</v>
+      </c>
+      <c r="C335" t="s">
+        <v>445</v>
+      </c>
+      <c r="D335" t="s">
+        <v>431</v>
+      </c>
+      <c r="E335" t="s">
+        <v>446</v>
+      </c>
+      <c r="F335">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>458</v>
+      </c>
+      <c r="B336" t="s">
+        <v>444</v>
+      </c>
+      <c r="C336" t="s">
+        <v>445</v>
+      </c>
+      <c r="D336" t="s">
+        <v>459</v>
+      </c>
+      <c r="E336" t="s">
+        <v>446</v>
+      </c>
+      <c r="F336">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>452</v>
+      </c>
+      <c r="B337" t="s">
+        <v>444</v>
+      </c>
+      <c r="C337" t="s">
+        <v>445</v>
+      </c>
+      <c r="D337" t="s">
+        <v>394</v>
+      </c>
+      <c r="E337" t="s">
+        <v>446</v>
+      </c>
+      <c r="F337">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>460</v>
+      </c>
+      <c r="B338" t="s">
+        <v>444</v>
+      </c>
+      <c r="C338" t="s">
+        <v>445</v>
+      </c>
+      <c r="D338" t="s">
+        <v>66</v>
+      </c>
+      <c r="E338" t="s">
+        <v>446</v>
+      </c>
+      <c r="F338">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>461</v>
+      </c>
+      <c r="B339" t="s">
+        <v>444</v>
+      </c>
+      <c r="C339" t="s">
+        <v>445</v>
+      </c>
+      <c r="D339" t="s">
+        <v>264</v>
+      </c>
+      <c r="E339" t="s">
+        <v>446</v>
+      </c>
+      <c r="F339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>462</v>
+      </c>
+      <c r="B340" t="s">
+        <v>444</v>
+      </c>
+      <c r="C340" t="s">
+        <v>445</v>
+      </c>
+      <c r="D340" t="s">
+        <v>463</v>
+      </c>
+      <c r="E340" t="s">
+        <v>446</v>
+      </c>
+      <c r="F340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>457</v>
+      </c>
+      <c r="B341" t="s">
+        <v>444</v>
+      </c>
+      <c r="C341" t="s">
+        <v>445</v>
+      </c>
+      <c r="D341" t="s">
+        <v>374</v>
+      </c>
+      <c r="E341" t="s">
+        <v>446</v>
+      </c>
+      <c r="F341">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>252</v>
+      </c>
+      <c r="B342" t="s">
+        <v>444</v>
+      </c>
+      <c r="C342" t="s">
+        <v>445</v>
+      </c>
+      <c r="D342" t="s">
+        <v>349</v>
+      </c>
+      <c r="E342" t="s">
+        <v>446</v>
+      </c>
+      <c r="F342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>452</v>
+      </c>
+      <c r="B343" t="s">
+        <v>444</v>
+      </c>
+      <c r="C343" t="s">
+        <v>445</v>
+      </c>
+      <c r="D343" t="s">
+        <v>124</v>
+      </c>
+      <c r="E343" t="s">
+        <v>446</v>
+      </c>
+      <c r="F343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>464</v>
+      </c>
+      <c r="B344" t="s">
+        <v>444</v>
+      </c>
+      <c r="C344" t="s">
+        <v>445</v>
+      </c>
+      <c r="D344" t="s">
+        <v>66</v>
+      </c>
+      <c r="E344" t="s">
+        <v>446</v>
+      </c>
+      <c r="F344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>454</v>
+      </c>
+      <c r="B345" t="s">
+        <v>444</v>
+      </c>
+      <c r="C345" t="s">
+        <v>445</v>
+      </c>
+      <c r="D345" t="s">
+        <v>65</v>
+      </c>
+      <c r="E345" t="s">
+        <v>446</v>
+      </c>
+      <c r="F345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>465</v>
+      </c>
+      <c r="B346" t="s">
+        <v>444</v>
+      </c>
+      <c r="C346" t="s">
+        <v>445</v>
+      </c>
+      <c r="D346" t="s">
+        <v>455</v>
+      </c>
+      <c r="E346" t="s">
+        <v>446</v>
+      </c>
+      <c r="F346">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>449</v>
+      </c>
+      <c r="B347" t="s">
+        <v>444</v>
+      </c>
+      <c r="C347" t="s">
+        <v>445</v>
+      </c>
+      <c r="D347" t="s">
+        <v>337</v>
+      </c>
+      <c r="E347" t="s">
+        <v>446</v>
+      </c>
+      <c r="F347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>458</v>
+      </c>
+      <c r="B348" t="s">
+        <v>444</v>
+      </c>
+      <c r="C348" t="s">
+        <v>445</v>
+      </c>
+      <c r="D348" t="s">
+        <v>387</v>
+      </c>
+      <c r="E348" t="s">
+        <v>446</v>
+      </c>
+      <c r="F348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>466</v>
+      </c>
+      <c r="B349" t="s">
+        <v>444</v>
+      </c>
+      <c r="C349" t="s">
+        <v>445</v>
+      </c>
+      <c r="D349" t="s">
+        <v>414</v>
+      </c>
+      <c r="E349" t="s">
+        <v>446</v>
+      </c>
+      <c r="F349">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>442</v>
+      </c>
+      <c r="B350" t="s">
+        <v>444</v>
+      </c>
+      <c r="C350" t="s">
+        <v>445</v>
+      </c>
+      <c r="D350" t="s">
+        <v>467</v>
+      </c>
+      <c r="E350" t="s">
+        <v>446</v>
+      </c>
+      <c r="F350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>468</v>
+      </c>
+      <c r="B351" t="s">
+        <v>444</v>
+      </c>
+      <c r="C351" t="s">
+        <v>445</v>
+      </c>
+      <c r="D351" t="s">
+        <v>469</v>
+      </c>
+      <c r="E351" t="s">
+        <v>446</v>
+      </c>
+      <c r="F351">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>465</v>
+      </c>
+      <c r="B352" t="s">
+        <v>444</v>
+      </c>
+      <c r="C352" t="s">
+        <v>445</v>
+      </c>
+      <c r="D352" t="s">
+        <v>379</v>
+      </c>
+      <c r="E352" t="s">
+        <v>446</v>
+      </c>
+      <c r="F352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>457</v>
+      </c>
+      <c r="B353" t="s">
+        <v>444</v>
+      </c>
+      <c r="C353" t="s">
+        <v>445</v>
+      </c>
+      <c r="D353" t="s">
+        <v>310</v>
+      </c>
+      <c r="E353" t="s">
+        <v>446</v>
+      </c>
+      <c r="F353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>439</v>
+      </c>
+      <c r="B354" t="s">
+        <v>444</v>
+      </c>
+      <c r="C354" t="s">
+        <v>445</v>
+      </c>
+      <c r="D354" t="s">
+        <v>331</v>
+      </c>
+      <c r="E354" t="s">
+        <v>446</v>
+      </c>
+      <c r="F354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>470</v>
+      </c>
+      <c r="B355" t="s">
+        <v>444</v>
+      </c>
+      <c r="C355" t="s">
+        <v>445</v>
+      </c>
+      <c r="D355" t="s">
+        <v>59</v>
+      </c>
+      <c r="E355" t="s">
+        <v>446</v>
+      </c>
+      <c r="F355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>471</v>
+      </c>
+      <c r="B356" t="s">
+        <v>444</v>
+      </c>
+      <c r="C356" t="s">
+        <v>445</v>
+      </c>
+      <c r="D356" t="s">
+        <v>303</v>
+      </c>
+      <c r="E356" t="s">
+        <v>446</v>
+      </c>
+      <c r="F356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>472</v>
+      </c>
+      <c r="B357" t="s">
+        <v>444</v>
+      </c>
+      <c r="C357" t="s">
+        <v>445</v>
+      </c>
+      <c r="D357" t="s">
+        <v>473</v>
+      </c>
+      <c r="E357" t="s">
+        <v>446</v>
+      </c>
+      <c r="F357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>466</v>
+      </c>
+      <c r="B358" t="s">
+        <v>444</v>
+      </c>
+      <c r="C358" t="s">
+        <v>445</v>
+      </c>
+      <c r="D358" t="s">
+        <v>147</v>
+      </c>
+      <c r="E358" t="s">
+        <v>446</v>
+      </c>
+      <c r="F358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>474</v>
+      </c>
+      <c r="B359" t="s">
+        <v>444</v>
+      </c>
+      <c r="C359" t="s">
+        <v>445</v>
+      </c>
+      <c r="D359" t="s">
+        <v>475</v>
+      </c>
+      <c r="E359" t="s">
+        <v>446</v>
+      </c>
+      <c r="F359">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>468</v>
+      </c>
+      <c r="B360" t="s">
+        <v>444</v>
+      </c>
+      <c r="C360" t="s">
+        <v>445</v>
+      </c>
+      <c r="D360" t="s">
+        <v>476</v>
+      </c>
+      <c r="E360" t="s">
+        <v>446</v>
+      </c>
+      <c r="F360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>477</v>
+      </c>
+      <c r="B361" t="s">
+        <v>444</v>
+      </c>
+      <c r="C361" t="s">
+        <v>445</v>
+      </c>
+      <c r="D361" t="s">
+        <v>177</v>
+      </c>
+      <c r="E361" t="s">
+        <v>446</v>
+      </c>
+      <c r="F361">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>478</v>
+      </c>
+      <c r="B362" t="s">
+        <v>444</v>
+      </c>
+      <c r="C362" t="s">
+        <v>445</v>
+      </c>
+      <c r="D362" t="s">
+        <v>479</v>
+      </c>
+      <c r="E362" t="s">
+        <v>446</v>
+      </c>
+      <c r="F362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>458</v>
+      </c>
+      <c r="B363" t="s">
+        <v>444</v>
+      </c>
+      <c r="C363" t="s">
+        <v>445</v>
+      </c>
+      <c r="D363" t="s">
+        <v>480</v>
+      </c>
+      <c r="E363" t="s">
+        <v>446</v>
+      </c>
+      <c r="F363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>477</v>
+      </c>
+      <c r="B364" t="s">
+        <v>444</v>
+      </c>
+      <c r="C364" t="s">
+        <v>445</v>
+      </c>
+      <c r="D364" t="s">
+        <v>361</v>
+      </c>
+      <c r="E364" t="s">
+        <v>446</v>
+      </c>
+      <c r="F364">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>481</v>
+      </c>
+      <c r="B365" t="s">
+        <v>444</v>
+      </c>
+      <c r="C365" t="s">
+        <v>445</v>
+      </c>
+      <c r="D365" t="s">
+        <v>290</v>
+      </c>
+      <c r="E365" t="s">
+        <v>446</v>
+      </c>
+      <c r="F365">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>454</v>
+      </c>
+      <c r="B366" t="s">
+        <v>444</v>
+      </c>
+      <c r="C366" t="s">
+        <v>445</v>
+      </c>
+      <c r="D366" t="s">
+        <v>482</v>
+      </c>
+      <c r="E366" t="s">
+        <v>446</v>
+      </c>
+      <c r="F366">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>483</v>
+      </c>
+      <c r="B367" t="s">
+        <v>444</v>
+      </c>
+      <c r="C367" t="s">
+        <v>445</v>
+      </c>
+      <c r="D367" t="s">
+        <v>64</v>
+      </c>
+      <c r="E367" t="s">
+        <v>446</v>
+      </c>
+      <c r="F367">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>460</v>
+      </c>
+      <c r="B368" t="s">
+        <v>444</v>
+      </c>
+      <c r="C368" t="s">
+        <v>445</v>
+      </c>
+      <c r="D368" t="s">
+        <v>484</v>
+      </c>
+      <c r="E368" t="s">
+        <v>446</v>
+      </c>
+      <c r="F368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>436</v>
+      </c>
+      <c r="B369" t="s">
+        <v>444</v>
+      </c>
+      <c r="C369" t="s">
+        <v>445</v>
+      </c>
+      <c r="D369" t="s">
+        <v>383</v>
+      </c>
+      <c r="E369" t="s">
+        <v>446</v>
+      </c>
+      <c r="F369">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>452</v>
+      </c>
+      <c r="B370" t="s">
+        <v>444</v>
+      </c>
+      <c r="C370" t="s">
+        <v>445</v>
+      </c>
+      <c r="D370" t="s">
+        <v>485</v>
+      </c>
+      <c r="E370" t="s">
+        <v>446</v>
+      </c>
+      <c r="F370">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>457</v>
+      </c>
+      <c r="B371" t="s">
+        <v>444</v>
+      </c>
+      <c r="C371" t="s">
+        <v>445</v>
+      </c>
+      <c r="D371" t="s">
+        <v>486</v>
+      </c>
+      <c r="E371" t="s">
+        <v>446</v>
+      </c>
+      <c r="F371">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
